--- a/research/traditional_assets/database/data/kenya/kenya_beverage_alcoholic.xlsx
+++ b/research/traditional_assets/database/data/kenya/kenya_beverage_alcoholic.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1449177020756178</v>
+        <v>0.1445144489693909</v>
       </c>
       <c r="C2">
-        <v>1513.623823397514</v>
+        <v>1504.862124761589</v>
       </c>
       <c r="D2">
-        <v>1422.823823397514</v>
+        <v>1428.636124761589</v>
       </c>
       <c r="E2">
-        <v>-392</v>
+        <v>-377.426</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>14.574</v>
       </c>
       <c r="G2">
         <v>90.8</v>
@@ -1457,28 +1457,28 @@
         <v>293.6</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.7330722000000001</v>
       </c>
       <c r="N2">
-        <v>293.6</v>
+        <v>292.8669278</v>
       </c>
       <c r="O2">
-        <v>88.07999999999998</v>
+        <v>87.86007833999999</v>
       </c>
       <c r="P2">
-        <v>205.52</v>
+        <v>205.00684946</v>
       </c>
       <c r="Q2">
-        <v>260.92</v>
+        <v>260.40684946</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1449177020756178</v>
+        <v>0.1456185343125161</v>
       </c>
       <c r="T2">
-        <v>0.6910924838905985</v>
+        <v>0.6959789964029562</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>400.5062529993634</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1445144489693909</v>
+        <v>0.1441111958631641</v>
       </c>
       <c r="C3">
-        <v>1504.862124761589</v>
+        <v>1496.14810794987</v>
       </c>
       <c r="D3">
-        <v>1428.636124761589</v>
+        <v>1434.49610794987</v>
       </c>
       <c r="E3">
-        <v>-377.426</v>
+        <v>-362.852</v>
       </c>
       <c r="F3">
-        <v>14.574</v>
+        <v>29.148</v>
       </c>
       <c r="G3">
         <v>90.8</v>
@@ -1539,28 +1539,28 @@
         <v>293.6</v>
       </c>
       <c r="M3">
-        <v>0.7330722000000001</v>
+        <v>1.4661444</v>
       </c>
       <c r="N3">
-        <v>292.8669278</v>
+        <v>292.1338555999999</v>
       </c>
       <c r="O3">
-        <v>87.86007833999999</v>
+        <v>87.64015667999998</v>
       </c>
       <c r="P3">
-        <v>205.00684946</v>
+        <v>204.49369892</v>
       </c>
       <c r="Q3">
-        <v>260.40684946</v>
+        <v>259.89369892</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1456185343125161</v>
+        <v>0.1463336692481266</v>
       </c>
       <c r="T3">
-        <v>0.6959789964029562</v>
+        <v>0.7009652336604641</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>400.5062529993634</v>
+        <v>200.2531264996817</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1441111958631641</v>
+        <v>0.1437079427569372</v>
       </c>
       <c r="C4">
-        <v>1496.14810794987</v>
+        <v>1487.482362123254</v>
       </c>
       <c r="D4">
-        <v>1434.49610794987</v>
+        <v>1440.404362123254</v>
       </c>
       <c r="E4">
-        <v>-362.852</v>
+        <v>-348.278</v>
       </c>
       <c r="F4">
-        <v>29.148</v>
+        <v>43.722</v>
       </c>
       <c r="G4">
         <v>90.8</v>
@@ -1621,28 +1621,28 @@
         <v>293.6</v>
       </c>
       <c r="M4">
-        <v>1.4661444</v>
+        <v>2.1992166</v>
       </c>
       <c r="N4">
-        <v>292.1338555999999</v>
+        <v>291.4007834</v>
       </c>
       <c r="O4">
-        <v>87.64015667999998</v>
+        <v>87.42023501999999</v>
       </c>
       <c r="P4">
-        <v>204.49369892</v>
+        <v>203.98054838</v>
       </c>
       <c r="Q4">
-        <v>259.89369892</v>
+        <v>259.3805483799999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1463336692481266</v>
+        <v>0.1470635492339559</v>
       </c>
       <c r="T4">
-        <v>0.7009652336604641</v>
+        <v>0.7060542799335908</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>200.2531264996817</v>
+        <v>133.5020843331212</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1437079427569372</v>
+        <v>0.1433046896507104</v>
       </c>
       <c r="C5">
-        <v>1487.482362123254</v>
+        <v>1478.865486189078</v>
       </c>
       <c r="D5">
-        <v>1440.404362123254</v>
+        <v>1446.361486189078</v>
       </c>
       <c r="E5">
-        <v>-348.278</v>
+        <v>-333.704</v>
       </c>
       <c r="F5">
-        <v>43.722</v>
+        <v>58.29600000000001</v>
       </c>
       <c r="G5">
         <v>90.8</v>
@@ -1703,28 +1703,28 @@
         <v>293.6</v>
       </c>
       <c r="M5">
-        <v>2.1992166</v>
+        <v>2.9322888</v>
       </c>
       <c r="N5">
-        <v>291.4007834</v>
+        <v>290.6677112</v>
       </c>
       <c r="O5">
-        <v>87.42023501999999</v>
+        <v>87.20031336</v>
       </c>
       <c r="P5">
-        <v>203.98054838</v>
+        <v>203.46739784</v>
       </c>
       <c r="Q5">
-        <v>259.3805483799999</v>
+        <v>258.86739784</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1470635492339559</v>
+        <v>0.1478086350528233</v>
       </c>
       <c r="T5">
-        <v>0.7060542799335908</v>
+        <v>0.7112493480040742</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>133.5020843331212</v>
+        <v>100.1265632498409</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1433046896507104</v>
+        <v>0.1429014365444835</v>
       </c>
       <c r="C6">
-        <v>1478.865486189078</v>
+        <v>1470.298089003501</v>
       </c>
       <c r="D6">
-        <v>1446.361486189078</v>
+        <v>1452.368089003501</v>
       </c>
       <c r="E6">
-        <v>-333.704</v>
+        <v>-319.13</v>
       </c>
       <c r="F6">
-        <v>58.29600000000001</v>
+        <v>72.87</v>
       </c>
       <c r="G6">
         <v>90.8</v>
@@ -1785,28 +1785,28 @@
         <v>293.6</v>
       </c>
       <c r="M6">
-        <v>2.9322888</v>
+        <v>3.665361</v>
       </c>
       <c r="N6">
-        <v>290.6677112</v>
+        <v>289.9346389999999</v>
       </c>
       <c r="O6">
-        <v>87.20031336</v>
+        <v>86.98039169999998</v>
       </c>
       <c r="P6">
-        <v>203.46739784</v>
+        <v>202.9542473</v>
       </c>
       <c r="Q6">
-        <v>258.86739784</v>
+        <v>258.3542472999999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1478086350528233</v>
+        <v>0.14856940688893</v>
       </c>
       <c r="T6">
-        <v>0.7112493480040742</v>
+        <v>0.7165537859286731</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>100.1265632498409</v>
+        <v>80.10125059987269</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1429014365444835</v>
+        <v>0.1424981834382566</v>
       </c>
       <c r="C7">
-        <v>1470.298089003501</v>
+        <v>1461.780789578951</v>
       </c>
       <c r="D7">
-        <v>1452.368089003501</v>
+        <v>1458.424789578951</v>
       </c>
       <c r="E7">
-        <v>-319.13</v>
+        <v>-304.556</v>
       </c>
       <c r="F7">
-        <v>72.87</v>
+        <v>87.44400000000002</v>
       </c>
       <c r="G7">
         <v>90.8</v>
@@ -1867,28 +1867,28 @@
         <v>293.6</v>
       </c>
       <c r="M7">
-        <v>3.665361</v>
+        <v>4.3984332</v>
       </c>
       <c r="N7">
-        <v>289.9346389999999</v>
+        <v>289.2015668</v>
       </c>
       <c r="O7">
-        <v>86.98039169999998</v>
+        <v>86.76047003999999</v>
       </c>
       <c r="P7">
-        <v>202.9542473</v>
+        <v>202.44109676</v>
       </c>
       <c r="Q7">
-        <v>258.3542472999999</v>
+        <v>257.84109676</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.14856940688893</v>
+        <v>0.1493463653598475</v>
       </c>
       <c r="T7">
-        <v>0.7165537859286731</v>
+        <v>0.7219710842346465</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>80.10125059987269</v>
+        <v>66.75104216656057</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1424981834382566</v>
+        <v>0.1420949303320298</v>
       </c>
       <c r="C8">
-        <v>1461.780789578951</v>
+        <v>1453.314217296776</v>
       </c>
       <c r="D8">
-        <v>1458.424789578951</v>
+        <v>1464.532217296776</v>
       </c>
       <c r="E8">
-        <v>-304.556</v>
+        <v>-289.982</v>
       </c>
       <c r="F8">
-        <v>87.444</v>
+        <v>102.018</v>
       </c>
       <c r="G8">
         <v>90.8</v>
@@ -1949,28 +1949,28 @@
         <v>293.6</v>
       </c>
       <c r="M8">
-        <v>4.398433199999999</v>
+        <v>5.1315054</v>
       </c>
       <c r="N8">
-        <v>289.2015668</v>
+        <v>288.4684946</v>
       </c>
       <c r="O8">
-        <v>86.76047003999999</v>
+        <v>86.54054837999999</v>
       </c>
       <c r="P8">
-        <v>202.44109676</v>
+        <v>201.92794622</v>
       </c>
       <c r="Q8">
-        <v>257.84109676</v>
+        <v>257.3279462199999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1493463653598475</v>
+        <v>0.1501400326150858</v>
       </c>
       <c r="T8">
-        <v>0.7219710842346465</v>
+        <v>0.7275048835794581</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>66.75104216656058</v>
+        <v>57.21517899990907</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1420949303320298</v>
+        <v>0.141691677225803</v>
       </c>
       <c r="C9">
-        <v>1453.314217296776</v>
+        <v>1444.899012125273</v>
       </c>
       <c r="D9">
-        <v>1464.532217296776</v>
+        <v>1470.691012125273</v>
       </c>
       <c r="E9">
-        <v>-289.982</v>
+        <v>-275.408</v>
       </c>
       <c r="F9">
-        <v>102.018</v>
+        <v>116.592</v>
       </c>
       <c r="G9">
         <v>90.8</v>
@@ -2031,28 +2031,28 @@
         <v>293.6</v>
       </c>
       <c r="M9">
-        <v>5.131505400000001</v>
+        <v>5.864577600000001</v>
       </c>
       <c r="N9">
-        <v>288.4684946</v>
+        <v>287.7354223999999</v>
       </c>
       <c r="O9">
-        <v>86.54054837999999</v>
+        <v>86.32062671999998</v>
       </c>
       <c r="P9">
-        <v>201.92794622</v>
+        <v>201.41479568</v>
       </c>
       <c r="Q9">
-        <v>257.3279462199999</v>
+        <v>256.81479568</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1501400326150858</v>
+        <v>0.1509509535063076</v>
       </c>
       <c r="T9">
-        <v>0.7275048835794581</v>
+        <v>0.7331589829100263</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>57.21517899990906</v>
+        <v>50.06328162492042</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.141691677225803</v>
+        <v>0.1412884241195761</v>
       </c>
       <c r="C10">
-        <v>1444.899012125273</v>
+        <v>1436.53582484323</v>
       </c>
       <c r="D10">
-        <v>1470.691012125273</v>
+        <v>1476.90182484323</v>
       </c>
       <c r="E10">
-        <v>-275.408</v>
+        <v>-260.834</v>
       </c>
       <c r="F10">
-        <v>116.592</v>
+        <v>131.166</v>
       </c>
       <c r="G10">
         <v>90.8</v>
@@ -2113,28 +2113,28 @@
         <v>293.6</v>
       </c>
       <c r="M10">
-        <v>5.864577600000001</v>
+        <v>6.597649799999999</v>
       </c>
       <c r="N10">
-        <v>287.7354223999999</v>
+        <v>287.0023502</v>
       </c>
       <c r="O10">
-        <v>86.32062671999998</v>
+        <v>86.10070505999998</v>
       </c>
       <c r="P10">
-        <v>201.41479568</v>
+        <v>200.90164514</v>
       </c>
       <c r="Q10">
-        <v>256.81479568</v>
+        <v>256.3016451399999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1509509535063076</v>
+        <v>0.151779696834699</v>
       </c>
       <c r="T10">
-        <v>0.7331589829100263</v>
+        <v>0.7389373481599476</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>50.06328162492042</v>
+        <v>44.50069477770705</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1412884241195761</v>
+        <v>0.1408851710133492</v>
       </c>
       <c r="C11">
-        <v>1436.53582484323</v>
+        <v>1428.225317269158</v>
       </c>
       <c r="D11">
-        <v>1476.90182484323</v>
+        <v>1483.165317269158</v>
       </c>
       <c r="E11">
-        <v>-260.834</v>
+        <v>-246.26</v>
       </c>
       <c r="F11">
-        <v>131.166</v>
+        <v>145.74</v>
       </c>
       <c r="G11">
         <v>90.8</v>
@@ -2195,28 +2195,28 @@
         <v>293.6</v>
       </c>
       <c r="M11">
-        <v>6.597649799999999</v>
+        <v>7.330722</v>
       </c>
       <c r="N11">
-        <v>287.0023502</v>
+        <v>286.269278</v>
       </c>
       <c r="O11">
-        <v>86.10070505999998</v>
+        <v>85.8807834</v>
       </c>
       <c r="P11">
-        <v>200.90164514</v>
+        <v>200.3884946</v>
       </c>
       <c r="Q11">
-        <v>256.3016451399999</v>
+        <v>255.7884946</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.151779696834699</v>
+        <v>0.1526268566814991</v>
       </c>
       <c r="T11">
-        <v>0.7389373481599476</v>
+        <v>0.7448441215265339</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>44.50069477770705</v>
+        <v>40.05062529993635</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1408851710133492</v>
+        <v>0.1404819179071224</v>
       </c>
       <c r="C12">
-        <v>1428.225317269158</v>
+        <v>1419.968162496389</v>
       </c>
       <c r="D12">
-        <v>1483.165317269158</v>
+        <v>1489.482162496389</v>
       </c>
       <c r="E12">
-        <v>-246.26</v>
+        <v>-231.686</v>
       </c>
       <c r="F12">
-        <v>145.74</v>
+        <v>160.314</v>
       </c>
       <c r="G12">
         <v>90.8</v>
@@ -2277,28 +2277,28 @@
         <v>293.6</v>
       </c>
       <c r="M12">
-        <v>7.330722</v>
+        <v>8.0637942</v>
       </c>
       <c r="N12">
-        <v>286.269278</v>
+        <v>285.5362057999999</v>
       </c>
       <c r="O12">
-        <v>85.8807834</v>
+        <v>85.66086173999999</v>
       </c>
       <c r="P12">
-        <v>200.3884946</v>
+        <v>199.87534406</v>
       </c>
       <c r="Q12">
-        <v>255.7884946</v>
+        <v>255.27534406</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1526268566814991</v>
+        <v>0.1534930538282274</v>
       </c>
       <c r="T12">
-        <v>0.7448441215265339</v>
+        <v>0.7508836313732683</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>40.05062529993635</v>
+        <v>36.40965936357849</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1404819179071224</v>
+        <v>0.1400786648008956</v>
       </c>
       <c r="C13">
-        <v>1419.968162496389</v>
+        <v>1411.765045134201</v>
       </c>
       <c r="D13">
-        <v>1489.482162496389</v>
+        <v>1495.853045134201</v>
       </c>
       <c r="E13">
-        <v>-231.686</v>
+        <v>-217.112</v>
       </c>
       <c r="F13">
-        <v>160.314</v>
+        <v>174.888</v>
       </c>
       <c r="G13">
         <v>90.8</v>
@@ -2359,28 +2359,28 @@
         <v>293.6</v>
       </c>
       <c r="M13">
-        <v>8.0637942</v>
+        <v>8.796866399999999</v>
       </c>
       <c r="N13">
-        <v>285.5362057999999</v>
+        <v>284.8031336</v>
       </c>
       <c r="O13">
-        <v>85.66086173999999</v>
+        <v>85.44094007999999</v>
       </c>
       <c r="P13">
-        <v>199.87534406</v>
+        <v>199.36219352</v>
       </c>
       <c r="Q13">
-        <v>255.27534406</v>
+        <v>254.76219352</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1534930538282274</v>
+        <v>0.1543789372737449</v>
       </c>
       <c r="T13">
-        <v>0.7508836313732683</v>
+        <v>0.7570604028074284</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>36.40965936357849</v>
+        <v>33.37552108328029</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1400786648008956</v>
+        <v>0.1396754116946687</v>
       </c>
       <c r="C14">
-        <v>1411.765045134201</v>
+        <v>1403.616661555157</v>
       </c>
       <c r="D14">
-        <v>1495.853045134201</v>
+        <v>1502.278661555157</v>
       </c>
       <c r="E14">
-        <v>-217.112</v>
+        <v>-202.538</v>
       </c>
       <c r="F14">
-        <v>174.888</v>
+        <v>189.462</v>
       </c>
       <c r="G14">
         <v>90.8</v>
@@ -2441,28 +2441,28 @@
         <v>293.6</v>
       </c>
       <c r="M14">
-        <v>8.796866399999999</v>
+        <v>9.529938600000001</v>
       </c>
       <c r="N14">
-        <v>284.8031336</v>
+        <v>284.0700614</v>
       </c>
       <c r="O14">
-        <v>85.44094007999999</v>
+        <v>85.22101841999999</v>
       </c>
       <c r="P14">
-        <v>199.36219352</v>
+        <v>198.84904298</v>
       </c>
       <c r="Q14">
-        <v>254.76219352</v>
+        <v>254.24904298</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1543789372737449</v>
+        <v>0.155285185855941</v>
       </c>
       <c r="T14">
-        <v>0.7570604028074284</v>
+        <v>0.7633791689872014</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>33.37552108328029</v>
+        <v>30.80817330764334</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1396754116946687</v>
+        <v>0.1392721585884418</v>
       </c>
       <c r="C15">
-        <v>1403.616661555157</v>
+        <v>1395.523720148848</v>
       </c>
       <c r="D15">
-        <v>1502.278661555157</v>
+        <v>1508.759720148848</v>
       </c>
       <c r="E15">
-        <v>-202.538</v>
+        <v>-187.964</v>
       </c>
       <c r="F15">
-        <v>189.462</v>
+        <v>204.036</v>
       </c>
       <c r="G15">
         <v>90.8</v>
@@ -2523,28 +2523,28 @@
         <v>293.6</v>
       </c>
       <c r="M15">
-        <v>9.529938600000001</v>
+        <v>10.2630108</v>
       </c>
       <c r="N15">
-        <v>284.0700614</v>
+        <v>283.3369891999999</v>
       </c>
       <c r="O15">
-        <v>85.22101841999999</v>
+        <v>85.00109675999998</v>
       </c>
       <c r="P15">
-        <v>198.84904298</v>
+        <v>198.33589244</v>
       </c>
       <c r="Q15">
-        <v>254.24904298</v>
+        <v>253.7358924399999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.155285185855941</v>
+        <v>0.1562125099865602</v>
       </c>
       <c r="T15">
-        <v>0.7633791689872014</v>
+        <v>0.7698448832176666</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>30.80817330764334</v>
+        <v>28.60758949995452</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1392721585884418</v>
+        <v>0.138868905482215</v>
       </c>
       <c r="C16">
-        <v>1395.523720148848</v>
+        <v>1387.486941582232</v>
       </c>
       <c r="D16">
-        <v>1508.759720148848</v>
+        <v>1515.296941582232</v>
       </c>
       <c r="E16">
-        <v>-187.964</v>
+        <v>-173.39</v>
       </c>
       <c r="F16">
-        <v>204.036</v>
+        <v>218.61</v>
       </c>
       <c r="G16">
         <v>90.8</v>
@@ -2605,28 +2605,28 @@
         <v>293.6</v>
       </c>
       <c r="M16">
-        <v>10.2630108</v>
+        <v>10.996083</v>
       </c>
       <c r="N16">
-        <v>283.3369891999999</v>
+        <v>282.603917</v>
       </c>
       <c r="O16">
-        <v>85.00109675999998</v>
+        <v>84.78117509999998</v>
       </c>
       <c r="P16">
-        <v>198.33589244</v>
+        <v>197.8227419</v>
       </c>
       <c r="Q16">
-        <v>253.7358924399999</v>
+        <v>253.2227419</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1562125099865602</v>
+        <v>0.1571616535084882</v>
       </c>
       <c r="T16">
-        <v>0.7698448832176666</v>
+        <v>0.7764627319006137</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>28.60758949995452</v>
+        <v>26.70041686662422</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.138868905482215</v>
+        <v>0.1384656523759881</v>
       </c>
       <c r="C17">
-        <v>1387.486941582232</v>
+        <v>1379.507059066776</v>
       </c>
       <c r="D17">
-        <v>1515.296941582232</v>
+        <v>1521.891059066776</v>
       </c>
       <c r="E17">
-        <v>-173.39</v>
+        <v>-158.816</v>
       </c>
       <c r="F17">
-        <v>218.61</v>
+        <v>233.184</v>
       </c>
       <c r="G17">
         <v>90.8</v>
@@ -2687,28 +2687,28 @@
         <v>293.6</v>
       </c>
       <c r="M17">
-        <v>10.996083</v>
+        <v>11.7291552</v>
       </c>
       <c r="N17">
-        <v>282.603917</v>
+        <v>281.8708448</v>
       </c>
       <c r="O17">
-        <v>84.78117509999998</v>
+        <v>84.56125343999999</v>
       </c>
       <c r="P17">
-        <v>197.8227419</v>
+        <v>197.30959136</v>
       </c>
       <c r="Q17">
-        <v>253.2227419</v>
+        <v>252.70959136</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1571616535084882</v>
+        <v>0.1581333956857001</v>
       </c>
       <c r="T17">
-        <v>0.7764627319006137</v>
+        <v>0.7832381484093449</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>26.70041686662423</v>
+        <v>25.03164081246021</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1384656523759881</v>
+        <v>0.1380623992697613</v>
       </c>
       <c r="C18">
-        <v>1379.507059066776</v>
+        <v>1371.584818632589</v>
       </c>
       <c r="D18">
-        <v>1521.891059066776</v>
+        <v>1528.542818632589</v>
       </c>
       <c r="E18">
-        <v>-158.816</v>
+        <v>-144.242</v>
       </c>
       <c r="F18">
-        <v>233.184</v>
+        <v>247.758</v>
       </c>
       <c r="G18">
         <v>90.8</v>
@@ -2769,28 +2769,28 @@
         <v>293.6</v>
       </c>
       <c r="M18">
-        <v>11.7291552</v>
+        <v>12.4622274</v>
       </c>
       <c r="N18">
-        <v>281.8708448</v>
+        <v>281.1377725999999</v>
       </c>
       <c r="O18">
-        <v>84.56125343999999</v>
+        <v>84.34133177999998</v>
       </c>
       <c r="P18">
-        <v>197.30959136</v>
+        <v>196.79644082</v>
       </c>
       <c r="Q18">
-        <v>252.70959136</v>
+        <v>252.19644082</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1581333956857001</v>
+        <v>0.1591285533370618</v>
       </c>
       <c r="T18">
-        <v>0.7832381484093449</v>
+        <v>0.7901768279664796</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>25.03164081246021</v>
+        <v>23.55919135290373</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1380623992697613</v>
+        <v>0.1376591461635344</v>
       </c>
       <c r="C19">
-        <v>1371.584818632589</v>
+        <v>1363.720979409797</v>
       </c>
       <c r="D19">
-        <v>1528.542818632589</v>
+        <v>1535.252979409797</v>
       </c>
       <c r="E19">
-        <v>-144.242</v>
+        <v>-129.6679999999999</v>
       </c>
       <c r="F19">
-        <v>247.758</v>
+        <v>262.3320000000001</v>
       </c>
       <c r="G19">
         <v>90.8</v>
@@ -2851,28 +2851,28 @@
         <v>293.6</v>
       </c>
       <c r="M19">
-        <v>12.4622274</v>
+        <v>13.1952996</v>
       </c>
       <c r="N19">
-        <v>281.1377725999999</v>
+        <v>280.4047004</v>
       </c>
       <c r="O19">
-        <v>84.34133177999998</v>
+        <v>84.12141011999999</v>
       </c>
       <c r="P19">
-        <v>196.79644082</v>
+        <v>196.28329028</v>
       </c>
       <c r="Q19">
-        <v>252.19644082</v>
+        <v>251.6832902799999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1591285533370618</v>
+        <v>0.1601479831262615</v>
       </c>
       <c r="T19">
-        <v>0.7901768279664796</v>
+        <v>0.7972847436103734</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>23.55919135290373</v>
+        <v>22.25034738885352</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1376591461635344</v>
+        <v>0.1372558930573076</v>
       </c>
       <c r="C20">
-        <v>1363.720979409797</v>
+        <v>1355.91631391734</v>
       </c>
       <c r="D20">
-        <v>1535.252979409797</v>
+        <v>1542.02231391734</v>
       </c>
       <c r="E20">
-        <v>-129.668</v>
+        <v>-115.094</v>
       </c>
       <c r="F20">
-        <v>262.332</v>
+        <v>276.906</v>
       </c>
       <c r="G20">
         <v>90.8</v>
@@ -2933,28 +2933,28 @@
         <v>293.6</v>
       </c>
       <c r="M20">
-        <v>13.1952996</v>
+        <v>13.9283718</v>
       </c>
       <c r="N20">
-        <v>280.4047004</v>
+        <v>279.6716282</v>
       </c>
       <c r="O20">
-        <v>84.12141011999999</v>
+        <v>83.90148846</v>
       </c>
       <c r="P20">
-        <v>196.28329028</v>
+        <v>195.77013974</v>
       </c>
       <c r="Q20">
-        <v>251.6832902799999</v>
+        <v>251.17013974</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1601479831262615</v>
+        <v>0.1611925840213674</v>
       </c>
       <c r="T20">
-        <v>0.7972847436103734</v>
+        <v>0.80456816334424</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>22.25034738885353</v>
+        <v>21.07927647365071</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1372558930573076</v>
+        <v>0.1368526399510807</v>
       </c>
       <c r="C21">
-        <v>1355.91631391734</v>
+        <v>1348.17160835946</v>
       </c>
       <c r="D21">
-        <v>1542.02231391734</v>
+        <v>1548.85160835946</v>
       </c>
       <c r="E21">
-        <v>-115.094</v>
+        <v>-100.52</v>
       </c>
       <c r="F21">
-        <v>276.906</v>
+        <v>291.48</v>
       </c>
       <c r="G21">
         <v>90.8</v>
@@ -3015,28 +3015,28 @@
         <v>293.6</v>
       </c>
       <c r="M21">
-        <v>13.9283718</v>
+        <v>14.661444</v>
       </c>
       <c r="N21">
-        <v>279.6716282</v>
+        <v>278.9385559999999</v>
       </c>
       <c r="O21">
-        <v>83.90148846</v>
+        <v>83.68156679999998</v>
       </c>
       <c r="P21">
-        <v>195.77013974</v>
+        <v>195.2569892</v>
       </c>
       <c r="Q21">
-        <v>251.17013974</v>
+        <v>250.6569891999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1611925840213674</v>
+        <v>0.1622632999388509</v>
       </c>
       <c r="T21">
-        <v>0.80456816334424</v>
+        <v>0.8120336685714533</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>21.07927647365071</v>
+        <v>20.02531264996817</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1368526399510807</v>
+        <v>0.1364493868448539</v>
       </c>
       <c r="C22">
-        <v>1348.17160835946</v>
+        <v>1340.487662930092</v>
       </c>
       <c r="D22">
-        <v>1548.85160835946</v>
+        <v>1555.741662930093</v>
       </c>
       <c r="E22">
-        <v>-100.52</v>
+        <v>-85.94599999999997</v>
       </c>
       <c r="F22">
-        <v>291.48</v>
+        <v>306.054</v>
       </c>
       <c r="G22">
         <v>90.8</v>
@@ -3097,28 +3097,28 @@
         <v>293.6</v>
       </c>
       <c r="M22">
-        <v>14.661444</v>
+        <v>15.3945162</v>
       </c>
       <c r="N22">
-        <v>278.9385559999999</v>
+        <v>278.2054838</v>
       </c>
       <c r="O22">
-        <v>83.68156679999998</v>
+        <v>83.46164513999999</v>
       </c>
       <c r="P22">
-        <v>195.2569892</v>
+        <v>194.74383866</v>
       </c>
       <c r="Q22">
-        <v>250.6569891999999</v>
+        <v>250.14383866</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1622632999388509</v>
+        <v>0.1633611225884226</v>
       </c>
       <c r="T22">
-        <v>0.8120336685714533</v>
+        <v>0.8196881739310011</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>20.02531264996817</v>
+        <v>19.07172633330302</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1364493868448538</v>
+        <v>0.136046133738627</v>
       </c>
       <c r="C23">
-        <v>1340.487662930093</v>
+        <v>1332.865292125422</v>
       </c>
       <c r="D23">
-        <v>1555.741662930093</v>
+        <v>1562.693292125422</v>
       </c>
       <c r="E23">
-        <v>-85.94599999999997</v>
+        <v>-71.37199999999996</v>
       </c>
       <c r="F23">
-        <v>306.054</v>
+        <v>320.628</v>
       </c>
       <c r="G23">
         <v>90.8</v>
@@ -3179,28 +3179,28 @@
         <v>293.6</v>
       </c>
       <c r="M23">
-        <v>15.3945162</v>
+        <v>16.1275884</v>
       </c>
       <c r="N23">
-        <v>278.2054838</v>
+        <v>277.4724116</v>
       </c>
       <c r="O23">
-        <v>83.46164513999999</v>
+        <v>83.24172347999999</v>
       </c>
       <c r="P23">
-        <v>194.74383866</v>
+        <v>194.23068812</v>
       </c>
       <c r="Q23">
-        <v>250.14383866</v>
+        <v>249.63068812</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1633611225884226</v>
+        <v>0.1644870945367013</v>
       </c>
       <c r="T23">
-        <v>0.8196881739310009</v>
+        <v>0.8275389486587423</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>19.07172633330302</v>
+        <v>18.20482968178925</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.136046133738627</v>
+        <v>0.1356428806324001</v>
       </c>
       <c r="C24">
-        <v>1332.865292125422</v>
+        <v>1325.305325064859</v>
       </c>
       <c r="D24">
-        <v>1562.693292125422</v>
+        <v>1569.707325064859</v>
       </c>
       <c r="E24">
-        <v>-71.37199999999996</v>
+        <v>-56.79799999999994</v>
       </c>
       <c r="F24">
-        <v>320.628</v>
+        <v>335.2020000000001</v>
       </c>
       <c r="G24">
         <v>90.8</v>
@@ -3261,28 +3261,28 @@
         <v>293.6</v>
       </c>
       <c r="M24">
-        <v>16.1275884</v>
+        <v>16.8606606</v>
       </c>
       <c r="N24">
-        <v>277.4724116</v>
+        <v>276.7393393999999</v>
       </c>
       <c r="O24">
-        <v>83.24172347999999</v>
+        <v>83.02180181999998</v>
       </c>
       <c r="P24">
-        <v>194.23068812</v>
+        <v>193.71753758</v>
       </c>
       <c r="Q24">
-        <v>249.63068812</v>
+        <v>249.1175375799999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1644870945367013</v>
+        <v>0.1656423125096106</v>
       </c>
       <c r="T24">
-        <v>0.8275389486587423</v>
+        <v>0.8355936396131781</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>18.20482968178925</v>
+        <v>17.41331534779841</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1356428806324001</v>
+        <v>0.1352396275261733</v>
       </c>
       <c r="C25">
-        <v>1325.305325064859</v>
+        <v>1317.808605820686</v>
       </c>
       <c r="D25">
-        <v>1569.707325064859</v>
+        <v>1576.784605820686</v>
       </c>
       <c r="E25">
-        <v>-56.79799999999994</v>
+        <v>-42.22399999999993</v>
       </c>
       <c r="F25">
-        <v>335.2020000000001</v>
+        <v>349.7760000000001</v>
       </c>
       <c r="G25">
         <v>90.8</v>
@@ -3343,28 +3343,28 @@
         <v>293.6</v>
       </c>
       <c r="M25">
-        <v>16.8606606</v>
+        <v>17.5937328</v>
       </c>
       <c r="N25">
-        <v>276.7393393999999</v>
+        <v>276.0062672</v>
       </c>
       <c r="O25">
-        <v>83.02180181999998</v>
+        <v>82.80188015999998</v>
       </c>
       <c r="P25">
-        <v>193.71753758</v>
+        <v>193.20438704</v>
       </c>
       <c r="Q25">
-        <v>249.1175375799999</v>
+        <v>248.6043870399999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1656423125096106</v>
+        <v>0.1668279309554912</v>
       </c>
       <c r="T25">
-        <v>0.8355936396131781</v>
+        <v>0.8438602961190467</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>17.41331534779841</v>
+        <v>16.68776054164015</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1352396275261733</v>
+        <v>0.1348363744199464</v>
       </c>
       <c r="C26">
-        <v>1317.808605820686</v>
+        <v>1310.375993756688</v>
       </c>
       <c r="D26">
-        <v>1576.784605820686</v>
+        <v>1583.925993756688</v>
       </c>
       <c r="E26">
-        <v>-42.22399999999999</v>
+        <v>-27.64999999999998</v>
       </c>
       <c r="F26">
-        <v>349.776</v>
+        <v>364.35</v>
       </c>
       <c r="G26">
         <v>90.8</v>
@@ -3425,28 +3425,28 @@
         <v>293.6</v>
       </c>
       <c r="M26">
-        <v>17.5937328</v>
+        <v>18.326805</v>
       </c>
       <c r="N26">
-        <v>276.0062672</v>
+        <v>275.273195</v>
       </c>
       <c r="O26">
-        <v>82.80188015999998</v>
+        <v>82.5819585</v>
       </c>
       <c r="P26">
-        <v>193.20438704</v>
+        <v>192.6912365</v>
       </c>
       <c r="Q26">
-        <v>248.6043870399999</v>
+        <v>248.0912365</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1668279309554912</v>
+        <v>0.1680451658932619</v>
       </c>
       <c r="T26">
-        <v>0.8438602961190467</v>
+        <v>0.8523473967984049</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>16.68776054164015</v>
+        <v>16.02025011997454</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1348363744199464</v>
+        <v>0.1344331213137196</v>
       </c>
       <c r="C27">
-        <v>1310.375993756688</v>
+        <v>1303.008363875992</v>
       </c>
       <c r="D27">
-        <v>1583.925993756688</v>
+        <v>1591.132363875992</v>
       </c>
       <c r="E27">
-        <v>-27.64999999999998</v>
+        <v>-13.07599999999996</v>
       </c>
       <c r="F27">
-        <v>364.35</v>
+        <v>378.924</v>
       </c>
       <c r="G27">
         <v>90.8</v>
@@ -3507,28 +3507,28 @@
         <v>293.6</v>
       </c>
       <c r="M27">
-        <v>18.326805</v>
+        <v>19.0598772</v>
       </c>
       <c r="N27">
-        <v>275.273195</v>
+        <v>274.5401227999999</v>
       </c>
       <c r="O27">
-        <v>82.5819585</v>
+        <v>82.36203683999999</v>
       </c>
       <c r="P27">
-        <v>192.6912365</v>
+        <v>192.17808596</v>
       </c>
       <c r="Q27">
-        <v>248.0912365</v>
+        <v>247.57808596</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1680451658932619</v>
+        <v>0.169295299072594</v>
       </c>
       <c r="T27">
-        <v>0.8523473967984049</v>
+        <v>0.8610638785772051</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>16.02025011997454</v>
+        <v>15.40408665382167</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1344331213137196</v>
+        <v>0.1340298682074927</v>
       </c>
       <c r="C28">
-        <v>1303.008363875992</v>
+        <v>1295.706607178477</v>
       </c>
       <c r="D28">
-        <v>1591.132363875992</v>
+        <v>1598.404607178477</v>
       </c>
       <c r="E28">
-        <v>-13.07599999999996</v>
+        <v>1.498000000000047</v>
       </c>
       <c r="F28">
-        <v>378.924</v>
+        <v>393.498</v>
       </c>
       <c r="G28">
         <v>90.8</v>
@@ -3589,28 +3589,28 @@
         <v>293.6</v>
       </c>
       <c r="M28">
-        <v>19.0598772</v>
+        <v>19.7929494</v>
       </c>
       <c r="N28">
-        <v>274.5401227999999</v>
+        <v>273.8070506</v>
       </c>
       <c r="O28">
-        <v>82.36203683999999</v>
+        <v>82.14211517999999</v>
       </c>
       <c r="P28">
-        <v>192.17808596</v>
+        <v>191.66493542</v>
       </c>
       <c r="Q28">
-        <v>247.57808596</v>
+        <v>247.06493542</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.169295299072594</v>
+        <v>0.1705796824760175</v>
       </c>
       <c r="T28">
-        <v>0.8610638785772051</v>
+        <v>0.8700191680759727</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>15.40408665382167</v>
+        <v>14.83356492590235</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1340298682074927</v>
+        <v>0.1336266151012659</v>
       </c>
       <c r="C29">
-        <v>1295.706607178477</v>
+        <v>1288.471631028011</v>
       </c>
       <c r="D29">
-        <v>1598.404607178477</v>
+        <v>1605.743631028011</v>
       </c>
       <c r="E29">
-        <v>1.498000000000047</v>
+        <v>16.07200000000006</v>
       </c>
       <c r="F29">
-        <v>393.498</v>
+        <v>408.0720000000001</v>
       </c>
       <c r="G29">
         <v>90.8</v>
@@ -3671,28 +3671,28 @@
         <v>293.6</v>
       </c>
       <c r="M29">
-        <v>19.7929494</v>
+        <v>20.5260216</v>
       </c>
       <c r="N29">
-        <v>273.8070506</v>
+        <v>273.0739784</v>
       </c>
       <c r="O29">
-        <v>82.14211517999999</v>
+        <v>81.92219351999999</v>
       </c>
       <c r="P29">
-        <v>191.66493542</v>
+        <v>191.15178488</v>
       </c>
       <c r="Q29">
-        <v>247.06493542</v>
+        <v>246.55178488</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1705796824760175</v>
+        <v>0.1718997431962026</v>
       </c>
       <c r="T29">
-        <v>0.8700191680759727</v>
+        <v>0.8792232156163725</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>14.83356492590235</v>
+        <v>14.30379474997726</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1336266151012659</v>
+        <v>0.133223361995039</v>
       </c>
       <c r="C30">
-        <v>1288.471631028011</v>
+        <v>1281.304359529859</v>
       </c>
       <c r="D30">
-        <v>1605.743631028011</v>
+        <v>1613.150359529859</v>
       </c>
       <c r="E30">
-        <v>16.07200000000006</v>
+        <v>30.64600000000007</v>
       </c>
       <c r="F30">
-        <v>408.0720000000001</v>
+        <v>422.6460000000001</v>
       </c>
       <c r="G30">
         <v>90.8</v>
@@ -3753,28 +3753,28 @@
         <v>293.6</v>
       </c>
       <c r="M30">
-        <v>20.5260216</v>
+        <v>21.2590938</v>
       </c>
       <c r="N30">
-        <v>273.0739784</v>
+        <v>272.3409061999999</v>
       </c>
       <c r="O30">
-        <v>81.92219351999999</v>
+        <v>81.70227185999998</v>
       </c>
       <c r="P30">
-        <v>191.15178488</v>
+        <v>190.63863434</v>
       </c>
       <c r="Q30">
-        <v>246.55178488</v>
+        <v>246.0386343399999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1718997431962026</v>
+        <v>0.1732569887254071</v>
       </c>
       <c r="T30">
-        <v>0.8792232156163725</v>
+        <v>0.8886865321015726</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>14.30379474997726</v>
+        <v>13.81056044825391</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.133223361995039</v>
+        <v>0.1328201088888122</v>
       </c>
       <c r="C31">
-        <v>1281.304359529859</v>
+        <v>1274.205733918583</v>
       </c>
       <c r="D31">
-        <v>1613.150359529859</v>
+        <v>1620.625733918583</v>
       </c>
       <c r="E31">
-        <v>30.64600000000002</v>
+        <v>45.22000000000003</v>
       </c>
       <c r="F31">
-        <v>422.646</v>
+        <v>437.22</v>
       </c>
       <c r="G31">
         <v>90.8</v>
@@ -3835,28 +3835,28 @@
         <v>293.6</v>
       </c>
       <c r="M31">
-        <v>21.2590938</v>
+        <v>21.992166</v>
       </c>
       <c r="N31">
-        <v>272.3409061999999</v>
+        <v>271.607834</v>
       </c>
       <c r="O31">
-        <v>81.70227185999998</v>
+        <v>81.48235019999998</v>
       </c>
       <c r="P31">
-        <v>190.63863434</v>
+        <v>190.1254838</v>
       </c>
       <c r="Q31">
-        <v>246.0386343399999</v>
+        <v>245.5254838</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1732569887254071</v>
+        <v>0.1746530126983031</v>
       </c>
       <c r="T31">
-        <v>0.8886865321015726</v>
+        <v>0.8984202290577781</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>13.81056044825391</v>
+        <v>13.35020843331212</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1328201088888122</v>
+        <v>0.1324168557825853</v>
       </c>
       <c r="C32">
-        <v>1274.205733918583</v>
+        <v>1267.176712956777</v>
       </c>
       <c r="D32">
-        <v>1620.625733918583</v>
+        <v>1628.170712956777</v>
       </c>
       <c r="E32">
-        <v>45.22000000000003</v>
+        <v>59.79400000000004</v>
       </c>
       <c r="F32">
-        <v>437.22</v>
+        <v>451.794</v>
       </c>
       <c r="G32">
         <v>90.8</v>
@@ -3917,28 +3917,28 @@
         <v>293.6</v>
       </c>
       <c r="M32">
-        <v>21.992166</v>
+        <v>22.7252382</v>
       </c>
       <c r="N32">
-        <v>271.607834</v>
+        <v>270.8747618</v>
       </c>
       <c r="O32">
-        <v>81.48235019999998</v>
+        <v>81.26242853999999</v>
       </c>
       <c r="P32">
-        <v>190.1254838</v>
+        <v>189.61233326</v>
       </c>
       <c r="Q32">
-        <v>245.5254838</v>
+        <v>245.01233326</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1746530126983031</v>
+        <v>0.1760895011341816</v>
       </c>
       <c r="T32">
-        <v>0.8984202290577781</v>
+        <v>0.9084360621576417</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>13.35020843331212</v>
+        <v>12.91955654836656</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1324168557825853</v>
+        <v>0.1323496026763585</v>
       </c>
       <c r="C33">
-        <v>1267.176712956777</v>
+        <v>1253.867878070514</v>
       </c>
       <c r="D33">
-        <v>1628.170712956777</v>
+        <v>1629.435878070514</v>
       </c>
       <c r="E33">
-        <v>59.79400000000004</v>
+        <v>74.36800000000005</v>
       </c>
       <c r="F33">
-        <v>451.794</v>
+        <v>466.3680000000001</v>
       </c>
       <c r="G33">
         <v>90.8</v>
@@ -3999,45 +3999,45 @@
         <v>293.6</v>
       </c>
       <c r="M33">
-        <v>22.7252382</v>
+        <v>24.1578624</v>
       </c>
       <c r="N33">
-        <v>270.8747618</v>
+        <v>269.4421376</v>
       </c>
       <c r="O33">
-        <v>81.26242853999999</v>
+        <v>80.83264127999999</v>
       </c>
       <c r="P33">
-        <v>189.61233326</v>
+        <v>188.60949632</v>
       </c>
       <c r="Q33">
-        <v>245.01233326</v>
+        <v>244.00949632</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1760895011341816</v>
+        <v>0.1775682392299389</v>
       </c>
       <c r="T33">
-        <v>0.9084360621576417</v>
+        <v>0.9187464785839721</v>
       </c>
       <c r="U33">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V33">
         <v>0.3</v>
       </c>
       <c r="W33">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y33">
-        <v>12.91955654836656</v>
+        <v>12.15339317438947</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1323496026763585</v>
+        <v>0.1319568495701316</v>
       </c>
       <c r="C34">
-        <v>1253.867878070514</v>
+        <v>1246.721795940104</v>
       </c>
       <c r="D34">
-        <v>1629.435878070514</v>
+        <v>1636.863795940104</v>
       </c>
       <c r="E34">
-        <v>74.36800000000005</v>
+        <v>88.94200000000006</v>
       </c>
       <c r="F34">
-        <v>466.3680000000001</v>
+        <v>480.9420000000001</v>
       </c>
       <c r="G34">
         <v>90.8</v>
@@ -4081,28 +4081,28 @@
         <v>293.6</v>
       </c>
       <c r="M34">
-        <v>24.1578624</v>
+        <v>24.9127956</v>
       </c>
       <c r="N34">
-        <v>269.4421376</v>
+        <v>268.6872044</v>
       </c>
       <c r="O34">
-        <v>80.83264127999999</v>
+        <v>80.60616132</v>
       </c>
       <c r="P34">
-        <v>188.60949632</v>
+        <v>188.08104308</v>
       </c>
       <c r="Q34">
-        <v>244.00949632</v>
+        <v>243.4810430799999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1775682392299389</v>
+        <v>0.1790911187613905</v>
       </c>
       <c r="T34">
-        <v>0.9187464785839721</v>
+        <v>0.9293646686349691</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>12.15339317438947</v>
+        <v>11.7851085327413</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1319568495701316</v>
+        <v>0.1315640964639047</v>
       </c>
       <c r="C35">
-        <v>1246.721795940104</v>
+        <v>1239.643745490466</v>
       </c>
       <c r="D35">
-        <v>1636.863795940104</v>
+        <v>1644.359745490467</v>
       </c>
       <c r="E35">
-        <v>88.94200000000006</v>
+        <v>103.5160000000001</v>
       </c>
       <c r="F35">
-        <v>480.9420000000001</v>
+        <v>495.5160000000001</v>
       </c>
       <c r="G35">
         <v>90.8</v>
@@ -4163,28 +4163,28 @@
         <v>293.6</v>
       </c>
       <c r="M35">
-        <v>24.9127956</v>
+        <v>25.6677288</v>
       </c>
       <c r="N35">
-        <v>268.6872044</v>
+        <v>267.9322711999999</v>
       </c>
       <c r="O35">
-        <v>80.60616132</v>
+        <v>80.37968135999998</v>
       </c>
       <c r="P35">
-        <v>188.08104308</v>
+        <v>187.55258984</v>
       </c>
       <c r="Q35">
-        <v>243.4810430799999</v>
+        <v>242.9525898399999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1790911187613905</v>
+        <v>0.1806601461574315</v>
       </c>
       <c r="T35">
-        <v>0.9293646686349691</v>
+        <v>0.9403046220208446</v>
       </c>
       <c r="U35">
         <v>0.0518</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>11.7851085327413</v>
+        <v>11.43848769354303</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1315640964639047</v>
+        <v>0.1311713433576779</v>
       </c>
       <c r="C36">
-        <v>1239.643745490466</v>
+        <v>1232.634665666197</v>
       </c>
       <c r="D36">
-        <v>1644.359745490467</v>
+        <v>1651.924665666197</v>
       </c>
       <c r="E36">
-        <v>103.5160000000001</v>
+        <v>118.0900000000001</v>
       </c>
       <c r="F36">
-        <v>495.5160000000001</v>
+        <v>510.0900000000001</v>
       </c>
       <c r="G36">
         <v>90.8</v>
@@ -4245,28 +4245,28 @@
         <v>293.6</v>
       </c>
       <c r="M36">
-        <v>25.6677288</v>
+        <v>26.422662</v>
       </c>
       <c r="N36">
-        <v>267.9322711999999</v>
+        <v>267.177338</v>
       </c>
       <c r="O36">
-        <v>80.37968135999998</v>
+        <v>80.15320139999999</v>
       </c>
       <c r="P36">
-        <v>187.55258984</v>
+        <v>187.0241366</v>
       </c>
       <c r="Q36">
-        <v>242.9525898399999</v>
+        <v>242.4241365999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1806601461574315</v>
+        <v>0.1822774513195045</v>
       </c>
       <c r="T36">
-        <v>0.9403046220208446</v>
+        <v>0.9515811893570548</v>
       </c>
       <c r="U36">
         <v>0.0518</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>11.43848769354303</v>
+        <v>11.1116737594418</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1311713433576779</v>
+        <v>0.1307785902514511</v>
       </c>
       <c r="C37">
-        <v>1232.634665666197</v>
+        <v>1225.695512770313</v>
       </c>
       <c r="D37">
-        <v>1651.924665666197</v>
+        <v>1659.559512770313</v>
       </c>
       <c r="E37">
-        <v>118.0900000000001</v>
+        <v>132.6640000000001</v>
       </c>
       <c r="F37">
-        <v>510.0900000000001</v>
+        <v>524.6640000000001</v>
       </c>
       <c r="G37">
         <v>90.8</v>
@@ -4327,28 +4327,28 @@
         <v>293.6</v>
       </c>
       <c r="M37">
-        <v>26.422662</v>
+        <v>27.17759520000001</v>
       </c>
       <c r="N37">
-        <v>267.177338</v>
+        <v>266.4224048</v>
       </c>
       <c r="O37">
-        <v>80.15320139999999</v>
+        <v>79.92672143999999</v>
       </c>
       <c r="P37">
-        <v>187.0241366</v>
+        <v>186.49568336</v>
       </c>
       <c r="Q37">
-        <v>242.4241365999999</v>
+        <v>241.89568336</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1822774513195045</v>
+        <v>0.1839452972678923</v>
       </c>
       <c r="T37">
-        <v>0.9515811893570548</v>
+        <v>0.9632101494225217</v>
       </c>
       <c r="U37">
         <v>0.0518</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>11.1116737594418</v>
+        <v>10.80301615501286</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1307785902514511</v>
+        <v>0.1303858371452242</v>
       </c>
       <c r="C38">
-        <v>1225.695512770313</v>
+        <v>1218.827260867241</v>
       </c>
       <c r="D38">
-        <v>1659.559512770313</v>
+        <v>1667.265260867241</v>
       </c>
       <c r="E38">
-        <v>132.664</v>
+        <v>147.2380000000001</v>
       </c>
       <c r="F38">
-        <v>524.664</v>
+        <v>539.2380000000001</v>
       </c>
       <c r="G38">
         <v>90.8</v>
@@ -4409,28 +4409,28 @@
         <v>293.6</v>
       </c>
       <c r="M38">
-        <v>27.1775952</v>
+        <v>27.9325284</v>
       </c>
       <c r="N38">
-        <v>266.4224048</v>
+        <v>265.6674715999999</v>
       </c>
       <c r="O38">
-        <v>79.92672143999999</v>
+        <v>79.70024147999997</v>
       </c>
       <c r="P38">
-        <v>186.49568336</v>
+        <v>185.96723012</v>
       </c>
       <c r="Q38">
-        <v>241.89568336</v>
+        <v>241.3672301199999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1839452972678923</v>
+        <v>0.1856660907067051</v>
       </c>
       <c r="T38">
-        <v>0.9632101494225217</v>
+        <v>0.9752082828234</v>
       </c>
       <c r="U38">
         <v>0.0518</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>10.80301615501286</v>
+        <v>10.51104274541792</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1303858371452242</v>
+        <v>0.1299930840389973</v>
       </c>
       <c r="C39">
-        <v>1218.827260867241</v>
+        <v>1212.030902197097</v>
       </c>
       <c r="D39">
-        <v>1667.265260867241</v>
+        <v>1675.042902197097</v>
       </c>
       <c r="E39">
-        <v>147.2380000000001</v>
+        <v>161.812</v>
       </c>
       <c r="F39">
-        <v>539.2380000000001</v>
+        <v>553.812</v>
       </c>
       <c r="G39">
         <v>90.8</v>
@@ -4491,28 +4491,28 @@
         <v>293.6</v>
       </c>
       <c r="M39">
-        <v>27.9325284</v>
+        <v>28.6874616</v>
       </c>
       <c r="N39">
-        <v>265.6674715999999</v>
+        <v>264.9125384</v>
       </c>
       <c r="O39">
-        <v>79.70024147999997</v>
+        <v>79.47376151999998</v>
       </c>
       <c r="P39">
-        <v>185.96723012</v>
+        <v>185.43877688</v>
       </c>
       <c r="Q39">
-        <v>241.3672301199999</v>
+        <v>240.83877688</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1856660907067051</v>
+        <v>0.187442393611286</v>
       </c>
       <c r="T39">
-        <v>0.9752082828234</v>
+        <v>0.9875934527855972</v>
       </c>
       <c r="U39">
         <v>0.0518</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>10.51104274541792</v>
+        <v>10.2344363573806</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1299930840389973</v>
+        <v>0.1296003309327705</v>
       </c>
       <c r="C40">
-        <v>1212.030902197097</v>
+        <v>1205.307447601613</v>
       </c>
       <c r="D40">
-        <v>1675.042902197097</v>
+        <v>1682.893447601613</v>
       </c>
       <c r="E40">
-        <v>161.812</v>
+        <v>176.3860000000001</v>
       </c>
       <c r="F40">
-        <v>553.812</v>
+        <v>568.3860000000001</v>
       </c>
       <c r="G40">
         <v>90.8</v>
@@ -4573,28 +4573,28 @@
         <v>293.6</v>
       </c>
       <c r="M40">
-        <v>28.6874616</v>
+        <v>29.4423948</v>
       </c>
       <c r="N40">
-        <v>264.9125384</v>
+        <v>264.1576052</v>
       </c>
       <c r="O40">
-        <v>79.47376151999998</v>
+        <v>79.24728155999999</v>
       </c>
       <c r="P40">
-        <v>185.43877688</v>
+        <v>184.91032364</v>
       </c>
       <c r="Q40">
-        <v>240.83877688</v>
+        <v>240.31032364</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.187442393611286</v>
+        <v>0.1892769359553615</v>
       </c>
       <c r="T40">
-        <v>0.9875934527855972</v>
+        <v>1.000384693894096</v>
       </c>
       <c r="U40">
         <v>0.0518</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>10.2344363573806</v>
+        <v>9.972014912319564</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1296003309327705</v>
+        <v>0.1296835778265437</v>
       </c>
       <c r="C41">
-        <v>1205.307447601613</v>
+        <v>1189.063327469711</v>
       </c>
       <c r="D41">
-        <v>1682.893447601613</v>
+        <v>1681.223327469711</v>
       </c>
       <c r="E41">
-        <v>176.3860000000001</v>
+        <v>190.96</v>
       </c>
       <c r="F41">
-        <v>568.3860000000001</v>
+        <v>582.96</v>
       </c>
       <c r="G41">
         <v>90.8</v>
@@ -4655,45 +4655,45 @@
         <v>293.6</v>
       </c>
       <c r="M41">
-        <v>29.4423948</v>
+        <v>31.18836</v>
       </c>
       <c r="N41">
-        <v>264.1576052</v>
+        <v>262.41164</v>
       </c>
       <c r="O41">
-        <v>79.24728155999999</v>
+        <v>78.72349199999999</v>
       </c>
       <c r="P41">
-        <v>184.91032364</v>
+        <v>183.688148</v>
       </c>
       <c r="Q41">
-        <v>240.31032364</v>
+        <v>239.088148</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1892769359553615</v>
+        <v>0.1911726297109061</v>
       </c>
       <c r="T41">
-        <v>1.000384693894096</v>
+        <v>1.013602309706211</v>
       </c>
       <c r="U41">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V41">
         <v>0.3</v>
       </c>
       <c r="W41">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y41">
-        <v>9.972014912319564</v>
+        <v>9.413768470031767</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1296835778265437</v>
+        <v>0.1293027247203168</v>
       </c>
       <c r="C42">
-        <v>1189.063327469711</v>
+        <v>1182.1573302645</v>
       </c>
       <c r="D42">
-        <v>1681.223327469711</v>
+        <v>1688.891330264501</v>
       </c>
       <c r="E42">
-        <v>190.96</v>
+        <v>205.5340000000001</v>
       </c>
       <c r="F42">
-        <v>582.96</v>
+        <v>597.5340000000001</v>
       </c>
       <c r="G42">
         <v>90.8</v>
@@ -4737,28 +4737,28 @@
         <v>293.6</v>
       </c>
       <c r="M42">
-        <v>31.18836</v>
+        <v>31.968069</v>
       </c>
       <c r="N42">
-        <v>262.41164</v>
+        <v>261.631931</v>
       </c>
       <c r="O42">
-        <v>78.72349199999999</v>
+        <v>78.48957929999999</v>
       </c>
       <c r="P42">
-        <v>183.688148</v>
+        <v>183.1423516999999</v>
       </c>
       <c r="Q42">
-        <v>239.088148</v>
+        <v>238.5423516999999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1911726297109061</v>
+        <v>0.1931325842717234</v>
       </c>
       <c r="T42">
-        <v>1.013602309706211</v>
+        <v>1.027267980291618</v>
       </c>
       <c r="U42">
         <v>0.0535</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>9.413768470031767</v>
+        <v>9.184164361006601</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1293027247203168</v>
+        <v>0.1289218716140899</v>
       </c>
       <c r="C43">
-        <v>1182.1573302645</v>
+        <v>1175.321600550294</v>
       </c>
       <c r="D43">
-        <v>1688.891330264501</v>
+        <v>1696.629600550294</v>
       </c>
       <c r="E43">
-        <v>205.5340000000001</v>
+        <v>220.1080000000001</v>
       </c>
       <c r="F43">
-        <v>597.5340000000001</v>
+        <v>612.1080000000001</v>
       </c>
       <c r="G43">
         <v>90.8</v>
@@ -4819,28 +4819,28 @@
         <v>293.6</v>
       </c>
       <c r="M43">
-        <v>31.968069</v>
+        <v>32.747778</v>
       </c>
       <c r="N43">
-        <v>261.631931</v>
+        <v>260.852222</v>
       </c>
       <c r="O43">
-        <v>78.48957929999999</v>
+        <v>78.2556666</v>
       </c>
       <c r="P43">
-        <v>183.1423516999999</v>
+        <v>182.5965554</v>
       </c>
       <c r="Q43">
-        <v>238.5423516999999</v>
+        <v>237.9965554</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1931325842717234</v>
+        <v>0.1951601234725689</v>
       </c>
       <c r="T43">
-        <v>1.027267980291618</v>
+        <v>1.041404880897212</v>
       </c>
       <c r="U43">
         <v>0.0535</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>9.184164361006601</v>
+        <v>8.965493780982635</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1289218716140899</v>
+        <v>0.1285410185078631</v>
       </c>
       <c r="C44">
-        <v>1175.321600550294</v>
+        <v>1168.557108641188</v>
       </c>
       <c r="D44">
-        <v>1696.629600550294</v>
+        <v>1704.439108641188</v>
       </c>
       <c r="E44">
-        <v>220.1080000000001</v>
+        <v>234.682</v>
       </c>
       <c r="F44">
-        <v>612.1080000000001</v>
+        <v>626.682</v>
       </c>
       <c r="G44">
         <v>90.8</v>
@@ -4901,28 +4901,28 @@
         <v>293.6</v>
       </c>
       <c r="M44">
-        <v>32.747778</v>
+        <v>33.527487</v>
       </c>
       <c r="N44">
-        <v>260.852222</v>
+        <v>260.072513</v>
       </c>
       <c r="O44">
-        <v>78.2556666</v>
+        <v>78.02175389999998</v>
       </c>
       <c r="P44">
-        <v>182.5965554</v>
+        <v>182.0507591</v>
       </c>
       <c r="Q44">
-        <v>237.9965554</v>
+        <v>237.4507591</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1951601234725688</v>
+        <v>0.1972588043997598</v>
       </c>
       <c r="T44">
-        <v>1.041404880897212</v>
+        <v>1.056037813103002</v>
       </c>
       <c r="U44">
         <v>0.0535</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>8.965493780982635</v>
+        <v>8.756993925610946</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1285410185078631</v>
+        <v>0.1281601654016362</v>
       </c>
       <c r="C45">
-        <v>1168.557108641188</v>
+        <v>1161.864842799138</v>
       </c>
       <c r="D45">
-        <v>1704.439108641188</v>
+        <v>1712.320842799139</v>
       </c>
       <c r="E45">
-        <v>234.682</v>
+        <v>249.2560000000001</v>
       </c>
       <c r="F45">
-        <v>626.682</v>
+        <v>641.2560000000001</v>
       </c>
       <c r="G45">
         <v>90.8</v>
@@ -4983,28 +4983,28 @@
         <v>293.6</v>
       </c>
       <c r="M45">
-        <v>33.527487</v>
+        <v>34.307196</v>
       </c>
       <c r="N45">
-        <v>260.072513</v>
+        <v>259.2928039999999</v>
       </c>
       <c r="O45">
-        <v>78.02175389999998</v>
+        <v>77.78784119999997</v>
       </c>
       <c r="P45">
-        <v>182.0507591</v>
+        <v>181.5049628</v>
       </c>
       <c r="Q45">
-        <v>237.4507591</v>
+        <v>236.9049627999999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1972588043997598</v>
+        <v>0.1994324382172075</v>
       </c>
       <c r="T45">
-        <v>1.056037813103002</v>
+        <v>1.071193350030428</v>
       </c>
       <c r="U45">
         <v>0.0535</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>8.756993925610946</v>
+        <v>8.557971336392512</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1281601654016362</v>
+        <v>0.1277793122954094</v>
       </c>
       <c r="C46">
-        <v>1161.864842799138</v>
+        <v>1155.245809650861</v>
       </c>
       <c r="D46">
-        <v>1712.320842799139</v>
+        <v>1720.275809650861</v>
       </c>
       <c r="E46">
-        <v>249.2560000000001</v>
+        <v>263.83</v>
       </c>
       <c r="F46">
-        <v>641.2560000000001</v>
+        <v>655.83</v>
       </c>
       <c r="G46">
         <v>90.8</v>
@@ -5065,28 +5065,28 @@
         <v>293.6</v>
       </c>
       <c r="M46">
-        <v>34.307196</v>
+        <v>35.086905</v>
       </c>
       <c r="N46">
-        <v>259.2928039999999</v>
+        <v>258.513095</v>
       </c>
       <c r="O46">
-        <v>77.78784119999997</v>
+        <v>77.55392849999998</v>
       </c>
       <c r="P46">
-        <v>181.5049628</v>
+        <v>180.9591665</v>
       </c>
       <c r="Q46">
-        <v>236.9049627999999</v>
+        <v>236.3591665</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1994324382172075</v>
+        <v>0.2016851132643807</v>
       </c>
       <c r="T46">
-        <v>1.071193350030428</v>
+        <v>1.086899997391578</v>
       </c>
       <c r="U46">
         <v>0.0535</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>8.557971336392512</v>
+        <v>8.367794195583793</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1277793122954094</v>
+        <v>0.1273984591891825</v>
       </c>
       <c r="C47">
-        <v>1155.245809650861</v>
+        <v>1148.701034616415</v>
       </c>
       <c r="D47">
-        <v>1720.275809650861</v>
+        <v>1728.305034616415</v>
       </c>
       <c r="E47">
-        <v>263.83</v>
+        <v>278.4040000000001</v>
       </c>
       <c r="F47">
-        <v>655.83</v>
+        <v>670.4040000000001</v>
       </c>
       <c r="G47">
         <v>90.8</v>
@@ -5147,28 +5147,28 @@
         <v>293.6</v>
       </c>
       <c r="M47">
-        <v>35.086905</v>
+        <v>35.86661400000001</v>
       </c>
       <c r="N47">
-        <v>258.513095</v>
+        <v>257.7333859999999</v>
       </c>
       <c r="O47">
-        <v>77.55392849999998</v>
+        <v>77.32001579999998</v>
       </c>
       <c r="P47">
-        <v>180.9591665</v>
+        <v>180.4133702</v>
       </c>
       <c r="Q47">
-        <v>236.3591665</v>
+        <v>235.8133702</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2016851132643807</v>
+        <v>0.2040212207207084</v>
       </c>
       <c r="T47">
-        <v>1.086899997391578</v>
+        <v>1.10318837243277</v>
       </c>
       <c r="U47">
         <v>0.0535</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>8.367794195583793</v>
+        <v>8.18588562611458</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1273984591891825</v>
+        <v>0.1270176060829557</v>
       </c>
       <c r="C48">
-        <v>1148.701034616415</v>
+        <v>1142.231562349833</v>
       </c>
       <c r="D48">
-        <v>1728.305034616415</v>
+        <v>1736.409562349833</v>
       </c>
       <c r="E48">
-        <v>278.4040000000001</v>
+        <v>292.9780000000001</v>
       </c>
       <c r="F48">
-        <v>670.4040000000001</v>
+        <v>684.9780000000001</v>
       </c>
       <c r="G48">
         <v>90.8</v>
@@ -5229,28 +5229,28 @@
         <v>293.6</v>
       </c>
       <c r="M48">
-        <v>35.86661400000001</v>
+        <v>36.646323</v>
       </c>
       <c r="N48">
-        <v>257.7333859999999</v>
+        <v>256.953677</v>
       </c>
       <c r="O48">
-        <v>77.32001579999998</v>
+        <v>77.08610309999999</v>
       </c>
       <c r="P48">
-        <v>180.4133702</v>
+        <v>179.8675739</v>
       </c>
       <c r="Q48">
-        <v>235.8133702</v>
+        <v>235.2675738999999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2040212207207084</v>
+        <v>0.2064454831753881</v>
       </c>
       <c r="T48">
-        <v>1.10318837243277</v>
+        <v>1.120091403135895</v>
       </c>
       <c r="U48">
         <v>0.0535</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>8.18588562611458</v>
+        <v>8.011717846835547</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1270176060829557</v>
+        <v>0.1266367529767288</v>
       </c>
       <c r="C49">
-        <v>1142.231562349833</v>
+        <v>1135.838457192224</v>
       </c>
       <c r="D49">
-        <v>1736.409562349833</v>
+        <v>1744.590457192224</v>
       </c>
       <c r="E49">
-        <v>292.9780000000001</v>
+        <v>307.5520000000001</v>
       </c>
       <c r="F49">
-        <v>684.9780000000001</v>
+        <v>699.5520000000001</v>
       </c>
       <c r="G49">
         <v>90.8</v>
@@ -5311,28 +5311,28 @@
         <v>293.6</v>
       </c>
       <c r="M49">
-        <v>36.646323</v>
+        <v>37.42603200000001</v>
       </c>
       <c r="N49">
-        <v>256.953677</v>
+        <v>256.1739679999999</v>
       </c>
       <c r="O49">
-        <v>77.08610309999999</v>
+        <v>76.85219039999998</v>
       </c>
       <c r="P49">
-        <v>179.8675739</v>
+        <v>179.3217776</v>
       </c>
       <c r="Q49">
-        <v>235.2675738999999</v>
+        <v>234.7217775999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2064454831753881</v>
+        <v>0.2089629864937093</v>
       </c>
       <c r="T49">
-        <v>1.120091403135895</v>
+        <v>1.137644550404524</v>
       </c>
       <c r="U49">
         <v>0.0535</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>8.011717846835547</v>
+        <v>7.844807058359804</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1266367529767288</v>
+        <v>0.126255899870502</v>
       </c>
       <c r="C50">
-        <v>1135.838457192224</v>
+        <v>1129.522803637728</v>
       </c>
       <c r="D50">
-        <v>1744.590457192224</v>
+        <v>1752.848803637728</v>
       </c>
       <c r="E50">
-        <v>307.552</v>
+        <v>322.126</v>
       </c>
       <c r="F50">
-        <v>699.552</v>
+        <v>714.126</v>
       </c>
       <c r="G50">
         <v>90.8</v>
@@ -5393,28 +5393,28 @@
         <v>293.6</v>
       </c>
       <c r="M50">
-        <v>37.426032</v>
+        <v>38.205741</v>
       </c>
       <c r="N50">
-        <v>256.1739679999999</v>
+        <v>255.394259</v>
       </c>
       <c r="O50">
-        <v>76.85219039999998</v>
+        <v>76.61827769999999</v>
       </c>
       <c r="P50">
-        <v>179.3217776</v>
+        <v>178.7759813</v>
       </c>
       <c r="Q50">
-        <v>234.7217775999999</v>
+        <v>234.1759813</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2089629864937093</v>
+        <v>0.2115792154323568</v>
       </c>
       <c r="T50">
-        <v>1.137644550404524</v>
+        <v>1.15588605638957</v>
       </c>
       <c r="U50">
         <v>0.0535</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>7.844807058359805</v>
+        <v>7.684708955127975</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.126255899870502</v>
+        <v>0.1261550467642751</v>
       </c>
       <c r="C51">
-        <v>1129.522803637728</v>
+        <v>1117.148792981415</v>
       </c>
       <c r="D51">
-        <v>1752.848803637728</v>
+        <v>1755.048792981415</v>
       </c>
       <c r="E51">
-        <v>322.126</v>
+        <v>336.7</v>
       </c>
       <c r="F51">
-        <v>714.126</v>
+        <v>728.7</v>
       </c>
       <c r="G51">
         <v>90.8</v>
@@ -5475,45 +5475,45 @@
         <v>293.6</v>
       </c>
       <c r="M51">
-        <v>38.205741</v>
+        <v>39.56841</v>
       </c>
       <c r="N51">
-        <v>255.394259</v>
+        <v>254.03159</v>
       </c>
       <c r="O51">
-        <v>76.61827769999999</v>
+        <v>76.20947699999999</v>
       </c>
       <c r="P51">
-        <v>178.7759813</v>
+        <v>177.822113</v>
       </c>
       <c r="Q51">
-        <v>234.1759813</v>
+        <v>233.222113</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2115792154323568</v>
+        <v>0.2143000935285502</v>
       </c>
       <c r="T51">
-        <v>1.15588605638957</v>
+        <v>1.174857222614017</v>
       </c>
       <c r="U51">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V51">
         <v>0.3</v>
       </c>
       <c r="W51">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y51">
-        <v>7.684708955127975</v>
+        <v>7.420060598846402</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1261550467642751</v>
+        <v>0.1257797936580483</v>
       </c>
       <c r="C52">
-        <v>1117.148792981415</v>
+        <v>1110.809216715512</v>
       </c>
       <c r="D52">
-        <v>1755.048792981415</v>
+        <v>1763.283216715512</v>
       </c>
       <c r="E52">
-        <v>336.7</v>
+        <v>351.2740000000001</v>
       </c>
       <c r="F52">
-        <v>728.7</v>
+        <v>743.2740000000001</v>
       </c>
       <c r="G52">
         <v>90.8</v>
@@ -5557,28 +5557,28 @@
         <v>293.6</v>
       </c>
       <c r="M52">
-        <v>39.56841</v>
+        <v>40.35977820000001</v>
       </c>
       <c r="N52">
-        <v>254.03159</v>
+        <v>253.2402218</v>
       </c>
       <c r="O52">
-        <v>76.20947699999999</v>
+        <v>75.97206653999999</v>
       </c>
       <c r="P52">
-        <v>177.822113</v>
+        <v>177.26815526</v>
       </c>
       <c r="Q52">
-        <v>233.222113</v>
+        <v>232.66815526</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2143000935285502</v>
+        <v>0.2171320278735679</v>
       </c>
       <c r="T52">
-        <v>1.174857222614017</v>
+        <v>1.194602722153749</v>
       </c>
       <c r="U52">
         <v>0.0543</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>7.420060598846402</v>
+        <v>7.274569214555295</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1257797936580483</v>
+        <v>0.1254045405518214</v>
       </c>
       <c r="C53">
-        <v>1110.809216715512</v>
+        <v>1104.547274038416</v>
       </c>
       <c r="D53">
-        <v>1763.283216715512</v>
+        <v>1771.595274038416</v>
       </c>
       <c r="E53">
-        <v>351.2740000000001</v>
+        <v>365.8480000000001</v>
       </c>
       <c r="F53">
-        <v>743.2740000000001</v>
+        <v>757.8480000000001</v>
       </c>
       <c r="G53">
         <v>90.8</v>
@@ -5639,28 +5639,28 @@
         <v>293.6</v>
       </c>
       <c r="M53">
-        <v>40.35977820000001</v>
+        <v>41.1511464</v>
       </c>
       <c r="N53">
-        <v>253.2402218</v>
+        <v>252.4488535999999</v>
       </c>
       <c r="O53">
-        <v>75.97206653999999</v>
+        <v>75.73465607999998</v>
       </c>
       <c r="P53">
-        <v>177.26815526</v>
+        <v>176.71419752</v>
       </c>
       <c r="Q53">
-        <v>232.66815526</v>
+        <v>232.1141975199999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2171320278735679</v>
+        <v>0.2200819594829612</v>
       </c>
       <c r="T53">
-        <v>1.194602722153749</v>
+        <v>1.215170950840969</v>
       </c>
       <c r="U53">
         <v>0.0543</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>7.274569214555295</v>
+        <v>7.134673652736924</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1254045405518214</v>
+        <v>0.1250292874455946</v>
       </c>
       <c r="C54">
-        <v>1104.547274038416</v>
+        <v>1098.364068036358</v>
       </c>
       <c r="D54">
-        <v>1771.595274038416</v>
+        <v>1779.986068036358</v>
       </c>
       <c r="E54">
-        <v>365.8480000000001</v>
+        <v>380.4220000000001</v>
       </c>
       <c r="F54">
-        <v>757.8480000000001</v>
+        <v>772.4220000000001</v>
       </c>
       <c r="G54">
         <v>90.8</v>
@@ -5721,28 +5721,28 @@
         <v>293.6</v>
       </c>
       <c r="M54">
-        <v>41.1511464</v>
+        <v>41.94251460000001</v>
       </c>
       <c r="N54">
-        <v>252.4488535999999</v>
+        <v>251.6574854</v>
       </c>
       <c r="O54">
-        <v>75.73465607999998</v>
+        <v>75.49724561999999</v>
       </c>
       <c r="P54">
-        <v>176.71419752</v>
+        <v>176.16023978</v>
       </c>
       <c r="Q54">
-        <v>232.1141975199999</v>
+        <v>231.56023978</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2200819594829612</v>
+        <v>0.2231574200970097</v>
       </c>
       <c r="T54">
-        <v>1.215170950840969</v>
+        <v>1.236614423302113</v>
       </c>
       <c r="U54">
         <v>0.0543</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>7.134673652736924</v>
+        <v>7.00005716872302</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1250292874455946</v>
+        <v>0.1246540343393677</v>
       </c>
       <c r="C55">
-        <v>1098.364068036358</v>
+        <v>1092.260722793177</v>
       </c>
       <c r="D55">
-        <v>1779.986068036358</v>
+        <v>1788.456722793177</v>
       </c>
       <c r="E55">
-        <v>380.4220000000001</v>
+        <v>394.9960000000001</v>
       </c>
       <c r="F55">
-        <v>772.4220000000001</v>
+        <v>786.9960000000001</v>
       </c>
       <c r="G55">
         <v>90.8</v>
@@ -5803,28 +5803,28 @@
         <v>293.6</v>
       </c>
       <c r="M55">
-        <v>41.94251460000001</v>
+        <v>42.7338828</v>
       </c>
       <c r="N55">
-        <v>251.6574854</v>
+        <v>250.8661172</v>
       </c>
       <c r="O55">
-        <v>75.49724561999999</v>
+        <v>75.25983515999998</v>
       </c>
       <c r="P55">
-        <v>176.16023978</v>
+        <v>175.60628204</v>
       </c>
       <c r="Q55">
-        <v>231.56023978</v>
+        <v>231.00628204</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2231574200970097</v>
+        <v>0.2263665963899298</v>
       </c>
       <c r="T55">
-        <v>1.236614423302113</v>
+        <v>1.258990220652873</v>
       </c>
       <c r="U55">
         <v>0.0543</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>7.00005716872302</v>
+        <v>6.870426480413335</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1246540343393677</v>
+        <v>0.1242787812331408</v>
       </c>
       <c r="C56">
-        <v>1092.260722793177</v>
+        <v>1086.238383892331</v>
       </c>
       <c r="D56">
-        <v>1788.456722793177</v>
+        <v>1797.008383892331</v>
       </c>
       <c r="E56">
-        <v>394.9960000000001</v>
+        <v>409.5700000000002</v>
       </c>
       <c r="F56">
-        <v>786.9960000000001</v>
+        <v>801.5700000000002</v>
       </c>
       <c r="G56">
         <v>90.8</v>
@@ -5885,28 +5885,28 @@
         <v>293.6</v>
       </c>
       <c r="M56">
-        <v>42.7338828</v>
+        <v>43.52525100000001</v>
       </c>
       <c r="N56">
-        <v>250.8661172</v>
+        <v>250.0747489999999</v>
       </c>
       <c r="O56">
-        <v>75.25983515999998</v>
+        <v>75.02242469999997</v>
       </c>
       <c r="P56">
-        <v>175.60628204</v>
+        <v>175.0523243</v>
       </c>
       <c r="Q56">
-        <v>231.00628204</v>
+        <v>230.4523242999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2263665963899298</v>
+        <v>0.229718402740313</v>
       </c>
       <c r="T56">
-        <v>1.258990220652873</v>
+        <v>1.282360497885888</v>
       </c>
       <c r="U56">
         <v>0.0543</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>6.870426480413335</v>
+        <v>6.745509635314909</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1242787812331408</v>
+        <v>0.123903528126914</v>
       </c>
       <c r="C57">
-        <v>1086.238383892331</v>
+        <v>1080.298218933374</v>
       </c>
       <c r="D57">
-        <v>1797.008383892331</v>
+        <v>1805.642218933375</v>
       </c>
       <c r="E57">
-        <v>409.5700000000002</v>
+        <v>424.1440000000001</v>
       </c>
       <c r="F57">
-        <v>801.5700000000002</v>
+        <v>816.1440000000001</v>
       </c>
       <c r="G57">
         <v>90.8</v>
@@ -5967,28 +5967,28 @@
         <v>293.6</v>
       </c>
       <c r="M57">
-        <v>43.52525100000001</v>
+        <v>44.31661920000001</v>
       </c>
       <c r="N57">
-        <v>250.0747489999999</v>
+        <v>249.2833808</v>
       </c>
       <c r="O57">
-        <v>75.02242469999997</v>
+        <v>74.78501424</v>
       </c>
       <c r="P57">
-        <v>175.0523243</v>
+        <v>174.49836656</v>
       </c>
       <c r="Q57">
-        <v>230.4523242999999</v>
+        <v>229.8983665599999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.229718402740313</v>
+        <v>0.2332225639248046</v>
       </c>
       <c r="T57">
-        <v>1.282360497885888</v>
+        <v>1.306793060447677</v>
       </c>
       <c r="U57">
         <v>0.0543</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>6.745509635314909</v>
+        <v>6.625054106112858</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.123903528126914</v>
+        <v>0.1235282750206871</v>
       </c>
       <c r="C58">
-        <v>1080.298218933374</v>
+        <v>1074.441418063405</v>
       </c>
       <c r="D58">
-        <v>1805.642218933375</v>
+        <v>1814.359418063405</v>
       </c>
       <c r="E58">
-        <v>424.1440000000001</v>
+        <v>438.7180000000002</v>
       </c>
       <c r="F58">
-        <v>816.1440000000001</v>
+        <v>830.7180000000002</v>
       </c>
       <c r="G58">
         <v>90.8</v>
@@ -6049,28 +6049,28 @@
         <v>293.6</v>
       </c>
       <c r="M58">
-        <v>44.31661920000001</v>
+        <v>45.10798740000001</v>
       </c>
       <c r="N58">
-        <v>249.2833808</v>
+        <v>248.4920126</v>
       </c>
       <c r="O58">
-        <v>74.78501424</v>
+        <v>74.54760377999999</v>
       </c>
       <c r="P58">
-        <v>174.49836656</v>
+        <v>173.94440882</v>
       </c>
       <c r="Q58">
-        <v>229.8983665599999</v>
+        <v>229.34440882</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2332225639248046</v>
+        <v>0.2368897093504352</v>
       </c>
       <c r="T58">
-        <v>1.306793060447677</v>
+        <v>1.332362021268154</v>
       </c>
       <c r="U58">
         <v>0.0543</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>6.625054106112858</v>
+        <v>6.508825086707368</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1235282750206871</v>
+        <v>0.1231530219144603</v>
       </c>
       <c r="C59">
-        <v>1074.441418063405</v>
+        <v>1068.66919452397</v>
       </c>
       <c r="D59">
-        <v>1814.359418063405</v>
+        <v>1823.16119452397</v>
       </c>
       <c r="E59">
-        <v>438.7180000000002</v>
+        <v>453.2920000000001</v>
       </c>
       <c r="F59">
-        <v>830.7180000000002</v>
+        <v>845.2920000000001</v>
       </c>
       <c r="G59">
         <v>90.8</v>
@@ -6131,28 +6131,28 @@
         <v>293.6</v>
       </c>
       <c r="M59">
-        <v>45.10798740000001</v>
+        <v>45.89935560000001</v>
       </c>
       <c r="N59">
-        <v>248.4920126</v>
+        <v>247.7006444</v>
       </c>
       <c r="O59">
-        <v>74.54760377999999</v>
+        <v>74.31019331999998</v>
       </c>
       <c r="P59">
-        <v>173.94440882</v>
+        <v>173.39045108</v>
       </c>
       <c r="Q59">
-        <v>229.34440882</v>
+        <v>228.79045108</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2368897093504352</v>
+        <v>0.240731480748715</v>
       </c>
       <c r="T59">
-        <v>1.332362021268154</v>
+        <v>1.35914855165151</v>
       </c>
       <c r="U59">
         <v>0.0543</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>6.508825086707368</v>
+        <v>6.396603964522759</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1231530219144603</v>
+        <v>0.1227777688082334</v>
       </c>
       <c r="C60">
-        <v>1068.66919452397</v>
+        <v>1062.982785213974</v>
       </c>
       <c r="D60">
-        <v>1823.161194523969</v>
+        <v>1832.048785213974</v>
       </c>
       <c r="E60">
-        <v>453.292</v>
+        <v>467.866</v>
       </c>
       <c r="F60">
-        <v>845.292</v>
+        <v>859.866</v>
       </c>
       <c r="G60">
         <v>90.8</v>
@@ -6213,28 +6213,28 @@
         <v>293.6</v>
       </c>
       <c r="M60">
-        <v>45.8993556</v>
+        <v>46.6907238</v>
       </c>
       <c r="N60">
-        <v>247.7006444</v>
+        <v>246.9092762</v>
       </c>
       <c r="O60">
-        <v>74.31019331999998</v>
+        <v>74.07278285999999</v>
       </c>
       <c r="P60">
-        <v>173.39045108</v>
+        <v>172.83649334</v>
       </c>
       <c r="Q60">
-        <v>228.79045108</v>
+        <v>228.23649334</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2407314807487149</v>
+        <v>0.2447606556298376</v>
       </c>
       <c r="T60">
-        <v>1.35914855165151</v>
+        <v>1.387241742053567</v>
       </c>
       <c r="U60">
         <v>0.0543</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>6.39660396452276</v>
+        <v>6.288186948174917</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1227777688082334</v>
+        <v>0.1224025157020066</v>
       </c>
       <c r="C61">
-        <v>1062.982785213974</v>
+        <v>1057.383451269134</v>
       </c>
       <c r="D61">
-        <v>1832.048785213974</v>
+        <v>1841.023451269135</v>
       </c>
       <c r="E61">
-        <v>467.866</v>
+        <v>482.4400000000001</v>
       </c>
       <c r="F61">
-        <v>859.866</v>
+        <v>874.4400000000001</v>
       </c>
       <c r="G61">
         <v>90.8</v>
@@ -6295,28 +6295,28 @@
         <v>293.6</v>
       </c>
       <c r="M61">
-        <v>46.6907238</v>
+        <v>47.482092</v>
       </c>
       <c r="N61">
-        <v>246.9092762</v>
+        <v>246.117908</v>
       </c>
       <c r="O61">
-        <v>74.07278285999999</v>
+        <v>73.83537239999998</v>
       </c>
       <c r="P61">
-        <v>172.83649334</v>
+        <v>172.2825356</v>
       </c>
       <c r="Q61">
-        <v>228.23649334</v>
+        <v>227.6825356</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2447606556298376</v>
+        <v>0.2489912892550164</v>
       </c>
       <c r="T61">
-        <v>1.387241742053567</v>
+        <v>1.416739591975727</v>
       </c>
       <c r="U61">
         <v>0.0543</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>6.288186948174917</v>
+        <v>6.183383832372002</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1224025157020066</v>
+        <v>0.1224542625957797</v>
       </c>
       <c r="C62">
-        <v>1057.383451269134</v>
+        <v>1041.566633952255</v>
       </c>
       <c r="D62">
-        <v>1841.023451269135</v>
+        <v>1839.780633952255</v>
       </c>
       <c r="E62">
-        <v>482.4400000000001</v>
+        <v>497.014</v>
       </c>
       <c r="F62">
-        <v>874.4400000000001</v>
+        <v>889.014</v>
       </c>
       <c r="G62">
         <v>90.8</v>
@@ -6377,45 +6377,45 @@
         <v>293.6</v>
       </c>
       <c r="M62">
-        <v>47.482092</v>
+        <v>49.16247420000001</v>
       </c>
       <c r="N62">
-        <v>246.117908</v>
+        <v>244.4375257999999</v>
       </c>
       <c r="O62">
-        <v>73.83537239999998</v>
+        <v>73.33125773999998</v>
       </c>
       <c r="P62">
-        <v>172.2825356</v>
+        <v>171.10626806</v>
       </c>
       <c r="Q62">
-        <v>227.6825356</v>
+        <v>226.5062680599999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2489912892550164</v>
+        <v>0.2534388784507172</v>
       </c>
       <c r="T62">
-        <v>1.416739591975727</v>
+        <v>1.447750152150305</v>
       </c>
       <c r="U62">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V62">
         <v>0.3</v>
       </c>
       <c r="W62">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y62">
-        <v>6.183383832372002</v>
+        <v>5.972034662161082</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1224542625957797</v>
+        <v>0.1220860094895529</v>
       </c>
       <c r="C63">
-        <v>1041.566633952255</v>
+        <v>1035.873750394998</v>
       </c>
       <c r="D63">
-        <v>1839.780633952255</v>
+        <v>1848.661750394998</v>
       </c>
       <c r="E63">
-        <v>497.014</v>
+        <v>511.5880000000001</v>
       </c>
       <c r="F63">
-        <v>889.014</v>
+        <v>903.5880000000001</v>
       </c>
       <c r="G63">
         <v>90.8</v>
@@ -6459,28 +6459,28 @@
         <v>293.6</v>
       </c>
       <c r="M63">
-        <v>49.16247420000001</v>
+        <v>49.96841640000001</v>
       </c>
       <c r="N63">
-        <v>244.4375257999999</v>
+        <v>243.6315835999999</v>
       </c>
       <c r="O63">
-        <v>73.33125773999998</v>
+        <v>73.08947507999999</v>
       </c>
       <c r="P63">
-        <v>171.10626806</v>
+        <v>170.5421085199999</v>
       </c>
       <c r="Q63">
-        <v>226.5062680599999</v>
+        <v>225.9421085199999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2534388784507172</v>
+        <v>0.258120551288297</v>
       </c>
       <c r="T63">
-        <v>1.447750152150305</v>
+        <v>1.480392847070914</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>5.972034662161082</v>
+        <v>5.875711522448806</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1220860094895529</v>
+        <v>0.121717756383326</v>
       </c>
       <c r="C64">
-        <v>1035.873750394998</v>
+        <v>1030.267025830646</v>
       </c>
       <c r="D64">
-        <v>1848.661750394998</v>
+        <v>1857.629025830646</v>
       </c>
       <c r="E64">
-        <v>511.5880000000001</v>
+        <v>526.162</v>
       </c>
       <c r="F64">
-        <v>903.5880000000001</v>
+        <v>918.162</v>
       </c>
       <c r="G64">
         <v>90.8</v>
@@ -6541,28 +6541,28 @@
         <v>293.6</v>
       </c>
       <c r="M64">
-        <v>49.96841640000001</v>
+        <v>50.77435860000001</v>
       </c>
       <c r="N64">
-        <v>243.6315835999999</v>
+        <v>242.8256414</v>
       </c>
       <c r="O64">
-        <v>73.08947507999999</v>
+        <v>72.84769241999999</v>
       </c>
       <c r="P64">
-        <v>170.5421085199999</v>
+        <v>169.97794898</v>
       </c>
       <c r="Q64">
-        <v>225.9421085199999</v>
+        <v>225.37794898</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.258120551288297</v>
+        <v>0.2630552875225027</v>
       </c>
       <c r="T64">
-        <v>1.480392847070914</v>
+        <v>1.514800011987231</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>5.875711522448806</v>
+        <v>5.782446260187715</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.121717756383326</v>
+        <v>0.1213495032770992</v>
       </c>
       <c r="C65">
-        <v>1030.267025830646</v>
+        <v>1024.747720160935</v>
       </c>
       <c r="D65">
-        <v>1857.629025830646</v>
+        <v>1866.683720160935</v>
       </c>
       <c r="E65">
-        <v>526.162</v>
+        <v>540.7360000000001</v>
       </c>
       <c r="F65">
-        <v>918.162</v>
+        <v>932.7360000000001</v>
       </c>
       <c r="G65">
         <v>90.8</v>
@@ -6623,28 +6623,28 @@
         <v>293.6</v>
       </c>
       <c r="M65">
-        <v>50.77435860000001</v>
+        <v>51.58030080000001</v>
       </c>
       <c r="N65">
-        <v>242.8256414</v>
+        <v>242.0196992</v>
       </c>
       <c r="O65">
-        <v>72.84769241999999</v>
+        <v>72.60590975999999</v>
       </c>
       <c r="P65">
-        <v>169.97794898</v>
+        <v>169.41378944</v>
       </c>
       <c r="Q65">
-        <v>225.37794898</v>
+        <v>224.8137894399999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2630552875225027</v>
+        <v>0.2682641757697199</v>
       </c>
       <c r="T65">
-        <v>1.514800011987231</v>
+        <v>1.551118686065566</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>5.782446260187715</v>
+        <v>5.692095537372281</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1213495032770992</v>
+        <v>0.1209812501708723</v>
       </c>
       <c r="C66">
-        <v>1024.747720160935</v>
+        <v>1019.317117972624</v>
       </c>
       <c r="D66">
-        <v>1866.683720160935</v>
+        <v>1875.827117972624</v>
       </c>
       <c r="E66">
-        <v>540.7360000000001</v>
+        <v>555.3100000000001</v>
       </c>
       <c r="F66">
-        <v>932.7360000000001</v>
+        <v>947.3100000000001</v>
       </c>
       <c r="G66">
         <v>90.8</v>
@@ -6705,28 +6705,28 @@
         <v>293.6</v>
       </c>
       <c r="M66">
-        <v>51.58030080000001</v>
+        <v>52.38624300000001</v>
       </c>
       <c r="N66">
-        <v>242.0196992</v>
+        <v>241.213757</v>
       </c>
       <c r="O66">
-        <v>72.60590975999999</v>
+        <v>72.36412709999999</v>
       </c>
       <c r="P66">
-        <v>169.41378944</v>
+        <v>168.8496299</v>
       </c>
       <c r="Q66">
-        <v>224.8137894399999</v>
+        <v>224.2496298999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2682641757697199</v>
+        <v>0.2737707147739208</v>
       </c>
       <c r="T66">
-        <v>1.551118686065566</v>
+        <v>1.589512712948376</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>5.692095537372281</v>
+        <v>5.604524836797323</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1209812501708723</v>
+        <v>0.1206129970646455</v>
       </c>
       <c r="C67">
-        <v>1019.317117972624</v>
+        <v>1013.976529145031</v>
       </c>
       <c r="D67">
-        <v>1875.827117972624</v>
+        <v>1885.060529145031</v>
       </c>
       <c r="E67">
-        <v>555.3100000000001</v>
+        <v>569.8840000000001</v>
       </c>
       <c r="F67">
-        <v>947.3100000000001</v>
+        <v>961.8840000000001</v>
       </c>
       <c r="G67">
         <v>90.8</v>
@@ -6787,28 +6787,28 @@
         <v>293.6</v>
       </c>
       <c r="M67">
-        <v>52.38624300000001</v>
+        <v>53.19218520000001</v>
       </c>
       <c r="N67">
-        <v>241.213757</v>
+        <v>240.4078148</v>
       </c>
       <c r="O67">
-        <v>72.36412709999999</v>
+        <v>72.12234443999998</v>
       </c>
       <c r="P67">
-        <v>168.8496299</v>
+        <v>168.28547036</v>
       </c>
       <c r="Q67">
-        <v>224.2496298999999</v>
+        <v>223.68547036</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2737707147739208</v>
+        <v>0.2796011678371925</v>
       </c>
       <c r="T67">
-        <v>1.589512712948376</v>
+        <v>1.630165212000765</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>5.604524836797323</v>
+        <v>5.519607793815545</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1206129970646455</v>
+        <v>0.1202447439584186</v>
       </c>
       <c r="C68">
-        <v>1013.976529145031</v>
+        <v>1008.727289475606</v>
       </c>
       <c r="D68">
-        <v>1885.060529145031</v>
+        <v>1894.385289475606</v>
       </c>
       <c r="E68">
-        <v>569.8840000000001</v>
+        <v>584.4580000000001</v>
       </c>
       <c r="F68">
-        <v>961.8840000000001</v>
+        <v>976.4580000000001</v>
       </c>
       <c r="G68">
         <v>90.8</v>
@@ -6869,28 +6869,28 @@
         <v>293.6</v>
       </c>
       <c r="M68">
-        <v>53.19218520000001</v>
+        <v>53.99812740000001</v>
       </c>
       <c r="N68">
-        <v>240.4078148</v>
+        <v>239.6018726</v>
       </c>
       <c r="O68">
-        <v>72.12234443999998</v>
+        <v>71.88056177999998</v>
       </c>
       <c r="P68">
-        <v>168.28547036</v>
+        <v>167.72131082</v>
       </c>
       <c r="Q68">
-        <v>223.68547036</v>
+        <v>223.12131082</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2796011678371925</v>
+        <v>0.2857849816921776</v>
       </c>
       <c r="T68">
-        <v>1.630165212000765</v>
+        <v>1.67328149887451</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>5.519607793815545</v>
+        <v>5.437225587937702</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1202447439584186</v>
+        <v>0.1198764908521917</v>
       </c>
       <c r="C69">
-        <v>1008.727289475606</v>
+        <v>1003.570761324155</v>
       </c>
       <c r="D69">
-        <v>1894.385289475606</v>
+        <v>1903.802761324156</v>
       </c>
       <c r="E69">
-        <v>584.4580000000001</v>
+        <v>599.0320000000002</v>
       </c>
       <c r="F69">
-        <v>976.4580000000001</v>
+        <v>991.0320000000002</v>
       </c>
       <c r="G69">
         <v>90.8</v>
@@ -6951,28 +6951,28 @@
         <v>293.6</v>
       </c>
       <c r="M69">
-        <v>53.99812740000001</v>
+        <v>54.80406960000001</v>
       </c>
       <c r="N69">
-        <v>239.6018726</v>
+        <v>238.7959303999999</v>
       </c>
       <c r="O69">
-        <v>71.88056177999998</v>
+        <v>71.63877911999998</v>
       </c>
       <c r="P69">
-        <v>167.72131082</v>
+        <v>167.15715128</v>
       </c>
       <c r="Q69">
-        <v>223.12131082</v>
+        <v>222.5571512799999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2857849816921776</v>
+        <v>0.2923552839130992</v>
       </c>
       <c r="T69">
-        <v>1.67328149887451</v>
+        <v>1.719092553677864</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>5.437225587937702</v>
+        <v>5.357266388115088</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1198764908521917</v>
+        <v>0.1195082377459649</v>
       </c>
       <c r="C70">
-        <v>1003.570761324155</v>
+        <v>998.5083342763834</v>
       </c>
       <c r="D70">
-        <v>1903.802761324156</v>
+        <v>1913.314334276384</v>
       </c>
       <c r="E70">
-        <v>599.0320000000002</v>
+        <v>613.6060000000001</v>
       </c>
       <c r="F70">
-        <v>991.0320000000002</v>
+        <v>1005.606</v>
       </c>
       <c r="G70">
         <v>90.8</v>
@@ -7033,28 +7033,28 @@
         <v>293.6</v>
       </c>
       <c r="M70">
-        <v>54.80406960000001</v>
+        <v>55.61001180000001</v>
       </c>
       <c r="N70">
-        <v>238.7959303999999</v>
+        <v>237.9899882</v>
       </c>
       <c r="O70">
-        <v>71.63877911999998</v>
+        <v>71.39699645999998</v>
       </c>
       <c r="P70">
-        <v>167.15715128</v>
+        <v>166.59299174</v>
       </c>
       <c r="Q70">
-        <v>222.5571512799999</v>
+        <v>221.99299174</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2923552839130992</v>
+        <v>0.2993494765998868</v>
       </c>
       <c r="T70">
-        <v>1.719092553677864</v>
+        <v>1.767859160404015</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>5.357266388115088</v>
+        <v>5.279624846258348</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1195082377459649</v>
+        <v>0.119139984639738</v>
       </c>
       <c r="C71">
-        <v>998.5083342763834</v>
+        <v>993.5414258274205</v>
       </c>
       <c r="D71">
-        <v>1913.314334276384</v>
+        <v>1922.921425827421</v>
       </c>
       <c r="E71">
-        <v>613.6060000000001</v>
+        <v>628.1800000000002</v>
       </c>
       <c r="F71">
-        <v>1005.606</v>
+        <v>1020.18</v>
       </c>
       <c r="G71">
         <v>90.8</v>
@@ -7115,28 +7115,28 @@
         <v>293.6</v>
       </c>
       <c r="M71">
-        <v>55.61001180000001</v>
+        <v>56.41595400000001</v>
       </c>
       <c r="N71">
-        <v>237.9899882</v>
+        <v>237.184046</v>
       </c>
       <c r="O71">
-        <v>71.39699645999998</v>
+        <v>71.15521379999998</v>
       </c>
       <c r="P71">
-        <v>166.59299174</v>
+        <v>166.0288322</v>
       </c>
       <c r="Q71">
-        <v>221.99299174</v>
+        <v>221.4288322</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2993494765998868</v>
+        <v>0.3068099487991269</v>
       </c>
       <c r="T71">
-        <v>1.767859160404015</v>
+        <v>1.819876874245243</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>5.279624846258348</v>
+        <v>5.204201634168943</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.119139984639738</v>
+        <v>0.1187717315335112</v>
       </c>
       <c r="C72">
-        <v>993.5414258274205</v>
+        <v>988.6714820860541</v>
       </c>
       <c r="D72">
-        <v>1922.921425827421</v>
+        <v>1932.625482086054</v>
       </c>
       <c r="E72">
-        <v>628.1800000000002</v>
+        <v>642.7540000000001</v>
       </c>
       <c r="F72">
-        <v>1020.18</v>
+        <v>1034.754</v>
       </c>
       <c r="G72">
         <v>90.8</v>
@@ -7197,28 +7197,28 @@
         <v>293.6</v>
       </c>
       <c r="M72">
-        <v>56.41595400000001</v>
+        <v>57.22189620000001</v>
       </c>
       <c r="N72">
-        <v>237.184046</v>
+        <v>236.3781038</v>
       </c>
       <c r="O72">
-        <v>71.15521379999998</v>
+        <v>70.91343113999999</v>
       </c>
       <c r="P72">
-        <v>166.0288322</v>
+        <v>165.46467266</v>
       </c>
       <c r="Q72">
-        <v>221.4288322</v>
+        <v>220.8646726599999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3068099487991269</v>
+        <v>0.3147849363224525</v>
       </c>
       <c r="T72">
-        <v>1.819876874245243</v>
+        <v>1.875482016627245</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>5.204201634168943</v>
+        <v>5.130903019603183</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1187717315335112</v>
+        <v>0.1184034784272843</v>
       </c>
       <c r="C73">
-        <v>988.6714820860543</v>
+        <v>983.899978500385</v>
       </c>
       <c r="D73">
-        <v>1932.625482086054</v>
+        <v>1942.427978500385</v>
       </c>
       <c r="E73">
-        <v>642.7539999999999</v>
+        <v>657.328</v>
       </c>
       <c r="F73">
-        <v>1034.754</v>
+        <v>1049.328</v>
       </c>
       <c r="G73">
         <v>90.8</v>
@@ -7279,28 +7279,28 @@
         <v>293.6</v>
       </c>
       <c r="M73">
-        <v>57.2218962</v>
+        <v>58.0278384</v>
       </c>
       <c r="N73">
-        <v>236.3781038</v>
+        <v>235.5721616</v>
       </c>
       <c r="O73">
-        <v>70.91343113999999</v>
+        <v>70.67164847999999</v>
       </c>
       <c r="P73">
-        <v>165.46467266</v>
+        <v>164.90051312</v>
       </c>
       <c r="Q73">
-        <v>220.8646726599999</v>
+        <v>220.3005131199999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3147849363224524</v>
+        <v>0.3233295658117297</v>
       </c>
       <c r="T73">
-        <v>1.875482016627245</v>
+        <v>1.935058954893676</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>5.130903019603184</v>
+        <v>5.059640477664251</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1184034784272843</v>
+        <v>0.1180352253210575</v>
       </c>
       <c r="C74">
-        <v>983.899978500385</v>
+        <v>979.22842060568</v>
       </c>
       <c r="D74">
-        <v>1942.427978500385</v>
+        <v>1952.33042060568</v>
       </c>
       <c r="E74">
-        <v>657.328</v>
+        <v>671.902</v>
       </c>
       <c r="F74">
-        <v>1049.328</v>
+        <v>1063.902</v>
       </c>
       <c r="G74">
         <v>90.8</v>
@@ -7361,28 +7361,28 @@
         <v>293.6</v>
       </c>
       <c r="M74">
-        <v>58.0278384</v>
+        <v>58.8337806</v>
       </c>
       <c r="N74">
-        <v>235.5721616</v>
+        <v>234.7662194</v>
       </c>
       <c r="O74">
-        <v>70.67164847999999</v>
+        <v>70.42986581999999</v>
       </c>
       <c r="P74">
-        <v>164.90051312</v>
+        <v>164.33635358</v>
       </c>
       <c r="Q74">
-        <v>220.3005131199999</v>
+        <v>219.73635358</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3233295658117297</v>
+        <v>0.3325071308187314</v>
       </c>
       <c r="T74">
-        <v>1.935058954893676</v>
+        <v>1.999048999698361</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>5.059640477664251</v>
+        <v>4.990330334134603</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1180352253210575</v>
+        <v>0.1176669722148306</v>
       </c>
       <c r="C75">
-        <v>979.22842060568</v>
+        <v>974.6583447952235</v>
       </c>
       <c r="D75">
-        <v>1952.33042060568</v>
+        <v>1962.334344795224</v>
       </c>
       <c r="E75">
-        <v>671.902</v>
+        <v>686.4760000000001</v>
       </c>
       <c r="F75">
-        <v>1063.902</v>
+        <v>1078.476</v>
       </c>
       <c r="G75">
         <v>90.8</v>
@@ -7443,28 +7443,28 @@
         <v>293.6</v>
       </c>
       <c r="M75">
-        <v>58.8337806</v>
+        <v>59.63972280000001</v>
       </c>
       <c r="N75">
-        <v>234.7662194</v>
+        <v>233.9602772</v>
       </c>
       <c r="O75">
-        <v>70.42986581999999</v>
+        <v>70.18808315999998</v>
       </c>
       <c r="P75">
-        <v>164.33635358</v>
+        <v>163.77219404</v>
       </c>
       <c r="Q75">
-        <v>219.73635358</v>
+        <v>219.17219404</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3325071308187314</v>
+        <v>0.3423906623647331</v>
       </c>
       <c r="T75">
-        <v>1.999048999698361</v>
+        <v>2.067961355641867</v>
       </c>
       <c r="U75">
         <v>0.0553</v>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>4.990330334134603</v>
+        <v>4.922893437727378</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1176669722148306</v>
+        <v>0.1172987191086038</v>
       </c>
       <c r="C76">
-        <v>974.6583447952235</v>
+        <v>970.1913191149847</v>
       </c>
       <c r="D76">
-        <v>1962.334344795224</v>
+        <v>1972.441319114985</v>
       </c>
       <c r="E76">
-        <v>686.4760000000001</v>
+        <v>701.0500000000002</v>
       </c>
       <c r="F76">
-        <v>1078.476</v>
+        <v>1093.05</v>
       </c>
       <c r="G76">
         <v>90.8</v>
@@ -7525,28 +7525,28 @@
         <v>293.6</v>
       </c>
       <c r="M76">
-        <v>59.63972280000001</v>
+        <v>60.44566500000001</v>
       </c>
       <c r="N76">
-        <v>233.9602772</v>
+        <v>233.1543349999999</v>
       </c>
       <c r="O76">
-        <v>70.18808315999998</v>
+        <v>69.94630049999998</v>
       </c>
       <c r="P76">
-        <v>163.77219404</v>
+        <v>163.2080345</v>
       </c>
       <c r="Q76">
-        <v>219.17219404</v>
+        <v>218.6080344999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3423906623647331</v>
+        <v>0.3530648764344151</v>
       </c>
       <c r="T76">
-        <v>2.067961355641867</v>
+        <v>2.142386700060855</v>
       </c>
       <c r="U76">
         <v>0.0553</v>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>4.922893437727378</v>
+        <v>4.857254858557679</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1172987191086038</v>
+        <v>0.1169304660023769</v>
       </c>
       <c r="C77">
-        <v>970.1913191149847</v>
+        <v>965.8289440829697</v>
       </c>
       <c r="D77">
-        <v>1972.441319114985</v>
+        <v>1982.65294408297</v>
       </c>
       <c r="E77">
-        <v>701.0500000000002</v>
+        <v>715.624</v>
       </c>
       <c r="F77">
-        <v>1093.05</v>
+        <v>1107.624</v>
       </c>
       <c r="G77">
         <v>90.8</v>
@@ -7607,28 +7607,28 @@
         <v>293.6</v>
       </c>
       <c r="M77">
-        <v>60.44566500000001</v>
+        <v>61.2516072</v>
       </c>
       <c r="N77">
-        <v>233.1543349999999</v>
+        <v>232.3483928</v>
       </c>
       <c r="O77">
-        <v>69.94630049999998</v>
+        <v>69.70451783999999</v>
       </c>
       <c r="P77">
-        <v>163.2080345</v>
+        <v>162.64387496</v>
       </c>
       <c r="Q77">
-        <v>218.6080344999999</v>
+        <v>218.04387496</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3530648764344151</v>
+        <v>0.3646286083432372</v>
       </c>
       <c r="T77">
-        <v>2.142386700060855</v>
+        <v>2.223014156514759</v>
       </c>
       <c r="U77">
         <v>0.0553</v>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>4.857254858557679</v>
+        <v>4.793343610418765</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1169304660023769</v>
+        <v>0.1165622128961501</v>
       </c>
       <c r="C78">
-        <v>965.8289440829697</v>
+        <v>961.5728535341602</v>
       </c>
       <c r="D78">
-        <v>1982.65294408297</v>
+        <v>1992.97085353416</v>
       </c>
       <c r="E78">
-        <v>715.624</v>
+        <v>730.1980000000001</v>
       </c>
       <c r="F78">
-        <v>1107.624</v>
+        <v>1122.198</v>
       </c>
       <c r="G78">
         <v>90.8</v>
@@ -7689,28 +7689,28 @@
         <v>293.6</v>
       </c>
       <c r="M78">
-        <v>61.2516072</v>
+        <v>62.05754940000001</v>
       </c>
       <c r="N78">
-        <v>232.3483928</v>
+        <v>231.5424506</v>
       </c>
       <c r="O78">
-        <v>69.70451783999999</v>
+        <v>69.46273517999998</v>
       </c>
       <c r="P78">
-        <v>162.64387496</v>
+        <v>162.07971542</v>
       </c>
       <c r="Q78">
-        <v>218.04387496</v>
+        <v>217.47971542</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3646286083432372</v>
+        <v>0.3771978821571743</v>
       </c>
       <c r="T78">
-        <v>2.223014156514759</v>
+        <v>2.310652696138566</v>
       </c>
       <c r="U78">
         <v>0.0553</v>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>4.793343610418765</v>
+        <v>4.73109239469904</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1165622128961501</v>
+        <v>0.1161939597899232</v>
       </c>
       <c r="C79">
-        <v>961.5728535341602</v>
+        <v>957.4247154919728</v>
       </c>
       <c r="D79">
-        <v>1992.97085353416</v>
+        <v>2003.396715491973</v>
       </c>
       <c r="E79">
-        <v>730.1980000000001</v>
+        <v>744.7720000000002</v>
       </c>
       <c r="F79">
-        <v>1122.198</v>
+        <v>1136.772</v>
       </c>
       <c r="G79">
         <v>90.8</v>
@@ -7771,28 +7771,28 @@
         <v>293.6</v>
       </c>
       <c r="M79">
-        <v>62.05754940000001</v>
+        <v>62.86349160000001</v>
       </c>
       <c r="N79">
-        <v>231.5424506</v>
+        <v>230.7365084</v>
       </c>
       <c r="O79">
-        <v>69.46273517999998</v>
+        <v>69.22095251999998</v>
       </c>
       <c r="P79">
-        <v>162.07971542</v>
+        <v>161.51555588</v>
       </c>
       <c r="Q79">
-        <v>217.47971542</v>
+        <v>216.9155558799999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3771978821571743</v>
+        <v>0.3909098172269238</v>
       </c>
       <c r="T79">
-        <v>2.310652696138566</v>
+        <v>2.406258375728175</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>4.73109239469904</v>
+        <v>4.670437363997769</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1161939597899232</v>
+        <v>0.1158257066836964</v>
       </c>
       <c r="C80">
-        <v>957.4247154919728</v>
+        <v>953.3862330672121</v>
       </c>
       <c r="D80">
-        <v>2003.396715491973</v>
+        <v>2013.932233067212</v>
       </c>
       <c r="E80">
-        <v>744.7720000000002</v>
+        <v>759.3460000000002</v>
       </c>
       <c r="F80">
-        <v>1136.772</v>
+        <v>1151.346</v>
       </c>
       <c r="G80">
         <v>90.8</v>
@@ -7853,28 +7853,28 @@
         <v>293.6</v>
       </c>
       <c r="M80">
-        <v>62.86349160000001</v>
+        <v>63.66943380000001</v>
       </c>
       <c r="N80">
-        <v>230.7365084</v>
+        <v>229.9305662</v>
       </c>
       <c r="O80">
-        <v>69.22095251999998</v>
+        <v>68.97916985999998</v>
       </c>
       <c r="P80">
-        <v>161.51555588</v>
+        <v>160.95139634</v>
       </c>
       <c r="Q80">
-        <v>216.9155558799999</v>
+        <v>216.35139634</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3909098172269238</v>
+        <v>0.4059276508747446</v>
       </c>
       <c r="T80">
-        <v>2.406258375728175</v>
+        <v>2.510969358135842</v>
       </c>
       <c r="U80">
         <v>0.0553</v>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>4.670437363997769</v>
+        <v>4.611317903694</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1158257066836964</v>
+        <v>0.1154574535774695</v>
       </c>
       <c r="C81">
-        <v>953.3862330672121</v>
+        <v>949.459145385541</v>
       </c>
       <c r="D81">
-        <v>2013.932233067212</v>
+        <v>2024.579145385541</v>
       </c>
       <c r="E81">
-        <v>759.3460000000002</v>
+        <v>773.9200000000001</v>
       </c>
       <c r="F81">
-        <v>1151.346</v>
+        <v>1165.92</v>
       </c>
       <c r="G81">
         <v>90.8</v>
@@ -7935,28 +7935,28 @@
         <v>293.6</v>
       </c>
       <c r="M81">
-        <v>63.66943380000001</v>
+        <v>64.47537600000001</v>
       </c>
       <c r="N81">
-        <v>229.9305662</v>
+        <v>229.124624</v>
       </c>
       <c r="O81">
-        <v>68.97916985999998</v>
+        <v>68.73738719999999</v>
       </c>
       <c r="P81">
-        <v>160.95139634</v>
+        <v>160.3872368</v>
       </c>
       <c r="Q81">
-        <v>216.35139634</v>
+        <v>215.7872368</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4059276508747446</v>
+        <v>0.4224472678873475</v>
       </c>
       <c r="T81">
-        <v>2.510969358135842</v>
+        <v>2.626151438784274</v>
       </c>
       <c r="U81">
         <v>0.0553</v>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>4.611317903694</v>
+        <v>4.553676429897825</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1154574535774695</v>
+        <v>0.1165067004712426</v>
       </c>
       <c r="C82">
-        <v>949.459145385541</v>
+        <v>904.8415517043786</v>
       </c>
       <c r="D82">
-        <v>2024.579145385541</v>
+        <v>1994.535551704379</v>
       </c>
       <c r="E82">
-        <v>773.9200000000001</v>
+        <v>788.4940000000001</v>
       </c>
       <c r="F82">
-        <v>1165.92</v>
+        <v>1180.494</v>
       </c>
       <c r="G82">
         <v>90.8</v>
@@ -8017,45 +8017,45 @@
         <v>293.6</v>
       </c>
       <c r="M82">
-        <v>64.47537600000001</v>
+        <v>68.23255320000001</v>
       </c>
       <c r="N82">
-        <v>229.124624</v>
+        <v>225.3674468</v>
       </c>
       <c r="O82">
-        <v>68.73738719999999</v>
+        <v>67.61023403999998</v>
       </c>
       <c r="P82">
-        <v>160.3872368</v>
+        <v>157.75721276</v>
       </c>
       <c r="Q82">
-        <v>215.7872368</v>
+        <v>213.1572127599999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4224472678873475</v>
+        <v>0.4407057919539088</v>
       </c>
       <c r="T82">
-        <v>2.626151438784274</v>
+        <v>2.753457948974648</v>
       </c>
       <c r="U82">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V82">
         <v>0.3</v>
       </c>
       <c r="W82">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y82">
-        <v>4.553676429897825</v>
+        <v>4.302931463511465</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1165067004712426</v>
+        <v>0.1161559473650158</v>
       </c>
       <c r="C83">
-        <v>904.8415517043786</v>
+        <v>900.2111252961122</v>
       </c>
       <c r="D83">
-        <v>1994.535551704379</v>
+        <v>2004.479125296112</v>
       </c>
       <c r="E83">
-        <v>788.4940000000001</v>
+        <v>803.0680000000002</v>
       </c>
       <c r="F83">
-        <v>1180.494</v>
+        <v>1195.068</v>
       </c>
       <c r="G83">
         <v>90.8</v>
@@ -8099,28 +8099,28 @@
         <v>293.6</v>
       </c>
       <c r="M83">
-        <v>68.23255320000001</v>
+        <v>69.07493040000001</v>
       </c>
       <c r="N83">
-        <v>225.3674468</v>
+        <v>224.5250695999999</v>
       </c>
       <c r="O83">
-        <v>67.61023403999998</v>
+        <v>67.35752087999998</v>
       </c>
       <c r="P83">
-        <v>157.75721276</v>
+        <v>157.16754872</v>
       </c>
       <c r="Q83">
-        <v>213.1572127599999</v>
+        <v>212.5675487199999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4407057919539088</v>
+        <v>0.4609930409167546</v>
       </c>
       <c r="T83">
-        <v>2.753457948974648</v>
+        <v>2.894909626963952</v>
       </c>
       <c r="U83">
         <v>0.0578</v>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>4.302931463511465</v>
+        <v>4.250456689566203</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1161559473650158</v>
+        <v>0.1158051942587889</v>
       </c>
       <c r="C84">
-        <v>900.2111252961122</v>
+        <v>895.6803411889996</v>
       </c>
       <c r="D84">
-        <v>2004.479125296112</v>
+        <v>2014.522341189</v>
       </c>
       <c r="E84">
-        <v>803.0680000000002</v>
+        <v>817.6420000000003</v>
       </c>
       <c r="F84">
-        <v>1195.068</v>
+        <v>1209.642</v>
       </c>
       <c r="G84">
         <v>90.8</v>
@@ -8181,28 +8181,28 @@
         <v>293.6</v>
       </c>
       <c r="M84">
-        <v>69.07493040000001</v>
+        <v>69.91730760000002</v>
       </c>
       <c r="N84">
-        <v>224.5250695999999</v>
+        <v>223.6826924</v>
       </c>
       <c r="O84">
-        <v>67.35752087999998</v>
+        <v>67.10480771999998</v>
       </c>
       <c r="P84">
-        <v>157.16754872</v>
+        <v>156.57788468</v>
       </c>
       <c r="Q84">
-        <v>212.5675487199999</v>
+        <v>211.9778846799999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4609930409167546</v>
+        <v>0.4836670250516998</v>
       </c>
       <c r="T84">
-        <v>2.894909626963952</v>
+        <v>3.053002678834351</v>
       </c>
       <c r="U84">
         <v>0.0578</v>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>4.250456689566203</v>
+        <v>4.199246368005165</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1158051942587889</v>
+        <v>0.1154544411525621</v>
       </c>
       <c r="C85">
-        <v>895.6803411889996</v>
+        <v>891.2507046645139</v>
       </c>
       <c r="D85">
-        <v>2014.522341189</v>
+        <v>2024.666704664514</v>
       </c>
       <c r="E85">
-        <v>817.6420000000003</v>
+        <v>832.2160000000001</v>
       </c>
       <c r="F85">
-        <v>1209.642</v>
+        <v>1224.216</v>
       </c>
       <c r="G85">
         <v>90.8</v>
@@ -8263,28 +8263,28 @@
         <v>293.6</v>
       </c>
       <c r="M85">
-        <v>69.91730760000002</v>
+        <v>70.75968480000002</v>
       </c>
       <c r="N85">
-        <v>223.6826924</v>
+        <v>222.8403152</v>
       </c>
       <c r="O85">
-        <v>67.10480771999998</v>
+        <v>66.85209455999998</v>
       </c>
       <c r="P85">
-        <v>156.57788468</v>
+        <v>155.98822064</v>
       </c>
       <c r="Q85">
-        <v>211.9778846799999</v>
+        <v>211.38822064</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4836670250516998</v>
+        <v>0.5091752572035133</v>
       </c>
       <c r="T85">
-        <v>3.053002678834351</v>
+        <v>3.23085736218855</v>
       </c>
       <c r="U85">
         <v>0.0578</v>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>4.199246368005165</v>
+        <v>4.149255339814627</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1154544411525621</v>
+        <v>0.1151036880463352</v>
       </c>
       <c r="C86">
-        <v>891.2507046645139</v>
+        <v>886.9237514776701</v>
       </c>
       <c r="D86">
-        <v>2024.666704664514</v>
+        <v>2034.91375147767</v>
       </c>
       <c r="E86">
-        <v>832.2160000000001</v>
+        <v>846.79</v>
       </c>
       <c r="F86">
-        <v>1224.216</v>
+        <v>1238.79</v>
       </c>
       <c r="G86">
         <v>90.8</v>
@@ -8345,28 +8345,28 @@
         <v>293.6</v>
       </c>
       <c r="M86">
-        <v>70.75968480000002</v>
+        <v>71.602062</v>
       </c>
       <c r="N86">
-        <v>222.8403152</v>
+        <v>221.997938</v>
       </c>
       <c r="O86">
-        <v>66.85209455999998</v>
+        <v>66.59938139999998</v>
       </c>
       <c r="P86">
-        <v>155.98822064</v>
+        <v>155.3985566</v>
       </c>
       <c r="Q86">
-        <v>211.38822064</v>
+        <v>210.7985566</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.509175257203513</v>
+        <v>0.5380845869755682</v>
       </c>
       <c r="T86">
-        <v>3.230857362188547</v>
+        <v>3.432426003323306</v>
       </c>
       <c r="U86">
         <v>0.0578</v>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>4.149255339814627</v>
+        <v>4.100440571110926</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1151036880463352</v>
+        <v>0.1147529349401084</v>
       </c>
       <c r="C87">
-        <v>886.9237514776701</v>
+        <v>882.7010486320914</v>
       </c>
       <c r="D87">
-        <v>2034.91375147767</v>
+        <v>2045.265048632092</v>
       </c>
       <c r="E87">
-        <v>846.79</v>
+        <v>861.364</v>
       </c>
       <c r="F87">
-        <v>1238.79</v>
+        <v>1253.364</v>
       </c>
       <c r="G87">
         <v>90.8</v>
@@ -8427,28 +8427,28 @@
         <v>293.6</v>
       </c>
       <c r="M87">
-        <v>71.602062</v>
+        <v>72.44443920000001</v>
       </c>
       <c r="N87">
-        <v>221.997938</v>
+        <v>221.1555608</v>
       </c>
       <c r="O87">
-        <v>66.59938139999998</v>
+        <v>66.34666823999999</v>
       </c>
       <c r="P87">
-        <v>155.3985566</v>
+        <v>154.80889256</v>
       </c>
       <c r="Q87">
-        <v>210.7985566</v>
+        <v>210.20889256</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5380845869755682</v>
+        <v>0.5711238210007741</v>
       </c>
       <c r="T87">
-        <v>3.432426003323306</v>
+        <v>3.662790164620171</v>
       </c>
       <c r="U87">
         <v>0.0578</v>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>4.100440571110926</v>
+        <v>4.052761029586381</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1147529349401084</v>
+        <v>0.1144021818338815</v>
       </c>
       <c r="C88">
-        <v>882.7010486320914</v>
+        <v>878.5841951788593</v>
       </c>
       <c r="D88">
-        <v>2045.265048632092</v>
+        <v>2055.722195178859</v>
       </c>
       <c r="E88">
-        <v>861.364</v>
+        <v>875.9380000000001</v>
       </c>
       <c r="F88">
-        <v>1253.364</v>
+        <v>1267.938</v>
       </c>
       <c r="G88">
         <v>90.8</v>
@@ -8509,28 +8509,28 @@
         <v>293.6</v>
       </c>
       <c r="M88">
-        <v>72.44443920000001</v>
+        <v>73.28681640000001</v>
       </c>
       <c r="N88">
-        <v>221.1555608</v>
+        <v>220.3131835999999</v>
       </c>
       <c r="O88">
-        <v>66.34666823999999</v>
+        <v>66.09395507999999</v>
       </c>
       <c r="P88">
-        <v>154.80889256</v>
+        <v>154.2192285199999</v>
       </c>
       <c r="Q88">
-        <v>210.20889256</v>
+        <v>209.6192285199999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5711238210007741</v>
+        <v>0.6092460141067809</v>
       </c>
       <c r="T88">
-        <v>3.662790164620171</v>
+        <v>3.928594966116556</v>
       </c>
       <c r="U88">
         <v>0.0578</v>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>4.052761029586381</v>
+        <v>4.006177569476192</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1144021818338815</v>
+        <v>0.1162074287276547</v>
       </c>
       <c r="C89">
-        <v>878.5841951788593</v>
+        <v>811.3014657965928</v>
       </c>
       <c r="D89">
-        <v>2055.722195178859</v>
+        <v>2003.013465796593</v>
       </c>
       <c r="E89">
-        <v>875.9380000000001</v>
+        <v>890.5120000000002</v>
       </c>
       <c r="F89">
-        <v>1267.938</v>
+        <v>1282.512</v>
       </c>
       <c r="G89">
         <v>90.8</v>
@@ -8591,45 +8591,45 @@
         <v>293.6</v>
       </c>
       <c r="M89">
-        <v>73.28681640000001</v>
+        <v>78.61798560000001</v>
       </c>
       <c r="N89">
-        <v>220.3131835999999</v>
+        <v>214.9820144</v>
       </c>
       <c r="O89">
-        <v>66.09395507999999</v>
+        <v>64.49460431999999</v>
       </c>
       <c r="P89">
-        <v>154.2192285199999</v>
+        <v>150.48741008</v>
       </c>
       <c r="Q89">
-        <v>209.6192285199999</v>
+        <v>205.8874100799999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.6092460141067809</v>
+        <v>0.6537219060637891</v>
       </c>
       <c r="T89">
-        <v>3.928594966116556</v>
+        <v>4.238700567862338</v>
       </c>
       <c r="U89">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V89">
         <v>0.3</v>
       </c>
       <c r="W89">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y89">
-        <v>4.006177569476192</v>
+        <v>3.73451440862153</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1162074287276547</v>
+        <v>0.1158811756214278</v>
       </c>
       <c r="C90">
-        <v>811.3014657965928</v>
+        <v>806.0522146929368</v>
       </c>
       <c r="D90">
-        <v>2003.013465796593</v>
+        <v>2012.338214692937</v>
       </c>
       <c r="E90">
-        <v>890.5120000000002</v>
+        <v>905.086</v>
       </c>
       <c r="F90">
-        <v>1282.512</v>
+        <v>1297.086</v>
       </c>
       <c r="G90">
         <v>90.8</v>
@@ -8673,28 +8673,28 @@
         <v>293.6</v>
       </c>
       <c r="M90">
-        <v>78.61798560000001</v>
+        <v>79.51137180000001</v>
       </c>
       <c r="N90">
-        <v>214.9820144</v>
+        <v>214.0886282</v>
       </c>
       <c r="O90">
-        <v>64.49460431999999</v>
+        <v>64.22658845999999</v>
       </c>
       <c r="P90">
-        <v>150.48741008</v>
+        <v>149.86203974</v>
       </c>
       <c r="Q90">
-        <v>205.8874100799999</v>
+        <v>205.2620397399999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6537219060637891</v>
+        <v>0.706284323831162</v>
       </c>
       <c r="T90">
-        <v>4.238700567862338</v>
+        <v>4.60518900628917</v>
       </c>
       <c r="U90">
         <v>0.0613</v>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>3.73451440862153</v>
+        <v>3.692553572569603</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1158811756214278</v>
+        <v>0.115554922515201</v>
       </c>
       <c r="C91">
-        <v>806.0522146929368</v>
+        <v>800.8901897858698</v>
       </c>
       <c r="D91">
-        <v>2012.338214692937</v>
+        <v>2021.75018978587</v>
       </c>
       <c r="E91">
-        <v>905.086</v>
+        <v>919.6600000000001</v>
       </c>
       <c r="F91">
-        <v>1297.086</v>
+        <v>1311.66</v>
       </c>
       <c r="G91">
         <v>90.8</v>
@@ -8755,28 +8755,28 @@
         <v>293.6</v>
       </c>
       <c r="M91">
-        <v>79.51137180000001</v>
+        <v>80.404758</v>
       </c>
       <c r="N91">
-        <v>214.0886282</v>
+        <v>213.195242</v>
       </c>
       <c r="O91">
-        <v>64.22658845999999</v>
+        <v>63.95857259999998</v>
       </c>
       <c r="P91">
-        <v>149.86203974</v>
+        <v>149.2366694</v>
       </c>
       <c r="Q91">
-        <v>205.2620397399999</v>
+        <v>204.6366694</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.706284323831162</v>
+        <v>0.7693592251520098</v>
       </c>
       <c r="T91">
-        <v>4.60518900628917</v>
+        <v>5.04497513240137</v>
       </c>
       <c r="U91">
         <v>0.0613</v>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>3.692553572569603</v>
+        <v>3.651525199541052</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.115554922515201</v>
+        <v>0.1152286694089741</v>
       </c>
       <c r="C92">
-        <v>800.8901897858698</v>
+        <v>795.8166207324427</v>
       </c>
       <c r="D92">
-        <v>2021.75018978587</v>
+        <v>2031.250620732443</v>
       </c>
       <c r="E92">
-        <v>919.6600000000001</v>
+        <v>934.2340000000002</v>
       </c>
       <c r="F92">
-        <v>1311.66</v>
+        <v>1326.234</v>
       </c>
       <c r="G92">
         <v>90.8</v>
@@ -8837,28 +8837,28 @@
         <v>293.6</v>
       </c>
       <c r="M92">
-        <v>80.404758</v>
+        <v>81.29814420000001</v>
       </c>
       <c r="N92">
-        <v>213.195242</v>
+        <v>212.3018557999999</v>
       </c>
       <c r="O92">
-        <v>63.95857259999998</v>
+        <v>63.69055673999998</v>
       </c>
       <c r="P92">
-        <v>149.2366694</v>
+        <v>148.61129906</v>
       </c>
       <c r="Q92">
-        <v>204.6366694</v>
+        <v>204.0112990599999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.7693592251520098</v>
+        <v>0.8464507712108237</v>
       </c>
       <c r="T92">
-        <v>5.04497513240137</v>
+        <v>5.582491508760724</v>
       </c>
       <c r="U92">
         <v>0.0613</v>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>3.651525199541052</v>
+        <v>3.611398548996644</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1152286694089741</v>
+        <v>0.1149024163027473</v>
       </c>
       <c r="C93">
-        <v>795.8166207324427</v>
+        <v>790.8327604120134</v>
       </c>
       <c r="D93">
-        <v>2031.250620732443</v>
+        <v>2040.840760412013</v>
       </c>
       <c r="E93">
-        <v>934.2340000000002</v>
+        <v>948.8080000000002</v>
       </c>
       <c r="F93">
-        <v>1326.234</v>
+        <v>1340.808</v>
       </c>
       <c r="G93">
         <v>90.8</v>
@@ -8919,28 +8919,28 @@
         <v>293.6</v>
       </c>
       <c r="M93">
-        <v>81.29814420000001</v>
+        <v>82.19153040000002</v>
       </c>
       <c r="N93">
-        <v>212.3018557999999</v>
+        <v>211.4084695999999</v>
       </c>
       <c r="O93">
-        <v>63.69055673999998</v>
+        <v>63.42254087999998</v>
       </c>
       <c r="P93">
-        <v>148.61129906</v>
+        <v>147.9859287199999</v>
       </c>
       <c r="Q93">
-        <v>204.0112990599999</v>
+        <v>203.3859287199999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.8464507712108237</v>
+        <v>0.9428152037843412</v>
       </c>
       <c r="T93">
-        <v>5.582491508760724</v>
+        <v>6.25438697920992</v>
       </c>
       <c r="U93">
         <v>0.0613</v>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>3.611398548996644</v>
+        <v>3.572144216942332</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1149024163027473</v>
+        <v>0.1145761631965204</v>
       </c>
       <c r="C94">
-        <v>790.8327604120134</v>
+        <v>785.9398854770484</v>
       </c>
       <c r="D94">
-        <v>2040.840760412013</v>
+        <v>2050.521885477048</v>
       </c>
       <c r="E94">
-        <v>948.8080000000002</v>
+        <v>963.3820000000001</v>
       </c>
       <c r="F94">
-        <v>1340.808</v>
+        <v>1355.382</v>
       </c>
       <c r="G94">
         <v>90.8</v>
@@ -9001,28 +9001,28 @@
         <v>293.6</v>
       </c>
       <c r="M94">
-        <v>82.19153040000002</v>
+        <v>83.0849166</v>
       </c>
       <c r="N94">
-        <v>211.4084695999999</v>
+        <v>210.5150834</v>
       </c>
       <c r="O94">
-        <v>63.42254087999998</v>
+        <v>63.15452501999999</v>
       </c>
       <c r="P94">
-        <v>147.9859287199999</v>
+        <v>147.36055838</v>
       </c>
       <c r="Q94">
-        <v>203.3859287199999</v>
+        <v>202.76055838</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.9428152037843412</v>
+        <v>1.066712331378864</v>
       </c>
       <c r="T94">
-        <v>6.25438697920992</v>
+        <v>7.118252584073169</v>
       </c>
       <c r="U94">
         <v>0.0613</v>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>3.572144216942332</v>
+        <v>3.533734064071985</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1145761631965204</v>
+        <v>0.1160923100902936</v>
       </c>
       <c r="C95">
-        <v>785.9398854770484</v>
+        <v>727.1378271974672</v>
       </c>
       <c r="D95">
-        <v>2050.521885477048</v>
+        <v>2006.293827197467</v>
       </c>
       <c r="E95">
-        <v>963.3820000000001</v>
+        <v>977.9560000000001</v>
       </c>
       <c r="F95">
-        <v>1355.382</v>
+        <v>1369.956</v>
       </c>
       <c r="G95">
         <v>90.8</v>
@@ -9083,45 +9083,45 @@
         <v>293.6</v>
       </c>
       <c r="M95">
-        <v>83.0849166</v>
+        <v>87.81417960000002</v>
       </c>
       <c r="N95">
-        <v>210.5150834</v>
+        <v>205.7858203999999</v>
       </c>
       <c r="O95">
-        <v>63.15452501999999</v>
+        <v>61.73574611999998</v>
       </c>
       <c r="P95">
-        <v>147.36055838</v>
+        <v>144.05007428</v>
       </c>
       <c r="Q95">
-        <v>202.76055838</v>
+        <v>199.4500742799999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.066712331378864</v>
+        <v>1.231908501504894</v>
       </c>
       <c r="T95">
-        <v>7.118252584073169</v>
+        <v>8.270073390557503</v>
       </c>
       <c r="U95">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V95">
         <v>0.3</v>
       </c>
       <c r="W95">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y95">
-        <v>3.533734064071985</v>
+        <v>3.34342359442825</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1160923100902936</v>
+        <v>0.1157856569840667</v>
       </c>
       <c r="C96">
-        <v>727.1378271974672</v>
+        <v>721.3547175116632</v>
       </c>
       <c r="D96">
-        <v>2006.293827197467</v>
+        <v>2015.084717511663</v>
       </c>
       <c r="E96">
-        <v>977.9560000000001</v>
+        <v>992.5300000000002</v>
       </c>
       <c r="F96">
-        <v>1369.956</v>
+        <v>1384.53</v>
       </c>
       <c r="G96">
         <v>90.8</v>
@@ -9165,28 +9165,28 @@
         <v>293.6</v>
       </c>
       <c r="M96">
-        <v>87.81417960000002</v>
+        <v>88.74837300000002</v>
       </c>
       <c r="N96">
-        <v>205.7858203999999</v>
+        <v>204.851627</v>
       </c>
       <c r="O96">
-        <v>61.73574611999998</v>
+        <v>61.45548809999998</v>
       </c>
       <c r="P96">
-        <v>144.05007428</v>
+        <v>143.3961389</v>
       </c>
       <c r="Q96">
-        <v>199.4500742799999</v>
+        <v>198.7961389</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.231908501504894</v>
+        <v>1.463183139681336</v>
       </c>
       <c r="T96">
-        <v>8.270073390557503</v>
+        <v>9.882622519635571</v>
       </c>
       <c r="U96">
         <v>0.0641</v>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>3.34342359442825</v>
+        <v>3.308229661855321</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1157856569840667</v>
+        <v>0.1154790038778399</v>
       </c>
       <c r="C97">
-        <v>721.3547175116632</v>
+        <v>715.6489841852012</v>
       </c>
       <c r="D97">
-        <v>2015.084717511663</v>
+        <v>2023.952984185202</v>
       </c>
       <c r="E97">
-        <v>992.5300000000002</v>
+        <v>1007.104</v>
       </c>
       <c r="F97">
-        <v>1384.53</v>
+        <v>1399.104</v>
       </c>
       <c r="G97">
         <v>90.8</v>
@@ -9247,28 +9247,28 @@
         <v>293.6</v>
       </c>
       <c r="M97">
-        <v>88.74837300000002</v>
+        <v>89.68256640000003</v>
       </c>
       <c r="N97">
-        <v>204.851627</v>
+        <v>203.9174335999999</v>
       </c>
       <c r="O97">
-        <v>61.45548809999998</v>
+        <v>61.17523007999998</v>
       </c>
       <c r="P97">
-        <v>143.3961389</v>
+        <v>142.7422035199999</v>
       </c>
       <c r="Q97">
-        <v>198.7961389</v>
+        <v>198.1422035199999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.463183139681336</v>
+        <v>1.810095096946</v>
       </c>
       <c r="T97">
-        <v>9.882622519635571</v>
+        <v>12.30144621325268</v>
       </c>
       <c r="U97">
         <v>0.0641</v>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>3.308229661855321</v>
+        <v>3.273768936210995</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1154790038778399</v>
+        <v>0.115172350771613</v>
       </c>
       <c r="C98">
-        <v>715.6489841852015</v>
+        <v>710.0216533200103</v>
       </c>
       <c r="D98">
-        <v>2023.952984185202</v>
+        <v>2032.89965332001</v>
       </c>
       <c r="E98">
-        <v>1007.104</v>
+        <v>1021.678</v>
       </c>
       <c r="F98">
-        <v>1399.104</v>
+        <v>1413.678</v>
       </c>
       <c r="G98">
         <v>90.8</v>
@@ -9329,28 +9329,28 @@
         <v>293.6</v>
       </c>
       <c r="M98">
-        <v>89.68256640000001</v>
+        <v>90.61675980000001</v>
       </c>
       <c r="N98">
-        <v>203.9174336</v>
+        <v>202.9832402</v>
       </c>
       <c r="O98">
-        <v>61.17523007999998</v>
+        <v>60.89497205999999</v>
       </c>
       <c r="P98">
-        <v>142.74220352</v>
+        <v>142.08826814</v>
       </c>
       <c r="Q98">
-        <v>198.14220352</v>
+        <v>197.4882681399999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.810095096945995</v>
+        <v>2.388281692387098</v>
       </c>
       <c r="T98">
-        <v>12.30144621325264</v>
+        <v>16.3328190359478</v>
       </c>
       <c r="U98">
         <v>0.0641</v>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>3.273768936210995</v>
+        <v>3.240018740992325</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.115172350771613</v>
+        <v>0.1148656976653861</v>
       </c>
       <c r="C99">
-        <v>710.0216533200103</v>
+        <v>704.4737692416702</v>
       </c>
       <c r="D99">
-        <v>2032.89965332001</v>
+        <v>2041.92576924167</v>
       </c>
       <c r="E99">
-        <v>1021.678</v>
+        <v>1036.252</v>
       </c>
       <c r="F99">
-        <v>1413.678</v>
+        <v>1428.252</v>
       </c>
       <c r="G99">
         <v>90.8</v>
@@ -9411,28 +9411,28 @@
         <v>293.6</v>
       </c>
       <c r="M99">
-        <v>90.61675980000001</v>
+        <v>91.55095320000001</v>
       </c>
       <c r="N99">
-        <v>202.9832402</v>
+        <v>202.0490468</v>
       </c>
       <c r="O99">
-        <v>60.89497205999999</v>
+        <v>60.61471403999998</v>
       </c>
       <c r="P99">
-        <v>142.08826814</v>
+        <v>141.43433276</v>
       </c>
       <c r="Q99">
-        <v>197.4882681399999</v>
+        <v>196.8343327599999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.388281692387098</v>
+        <v>3.544654883269304</v>
       </c>
       <c r="T99">
-        <v>16.3328190359478</v>
+        <v>24.3955646813381</v>
       </c>
       <c r="U99">
         <v>0.0641</v>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>3.240018740992325</v>
+        <v>3.206957325267914</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1148656976653861</v>
+        <v>0.1145590445591593</v>
       </c>
       <c r="C100">
-        <v>704.4737692416702</v>
+        <v>699.0063949057871</v>
       </c>
       <c r="D100">
-        <v>2041.92576924167</v>
+        <v>2051.032394905787</v>
       </c>
       <c r="E100">
-        <v>1036.252</v>
+        <v>1050.826</v>
       </c>
       <c r="F100">
-        <v>1428.252</v>
+        <v>1442.826</v>
       </c>
       <c r="G100">
         <v>90.8</v>
@@ -9493,28 +9493,28 @@
         <v>293.6</v>
       </c>
       <c r="M100">
-        <v>91.55095320000001</v>
+        <v>92.48514660000001</v>
       </c>
       <c r="N100">
-        <v>202.0490468</v>
+        <v>201.1148534</v>
       </c>
       <c r="O100">
-        <v>60.61471403999998</v>
+        <v>60.33445601999998</v>
       </c>
       <c r="P100">
-        <v>141.43433276</v>
+        <v>140.78039738</v>
       </c>
       <c r="Q100">
-        <v>196.8343327599999</v>
+        <v>196.18039738</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.544654883269304</v>
+        <v>7.013774455915923</v>
       </c>
       <c r="T100">
-        <v>24.3955646813381</v>
+        <v>48.58380161750903</v>
       </c>
       <c r="U100">
         <v>0.0641</v>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>3.206957325267914</v>
+        <v>3.174563816931874</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1145590445591593</v>
-      </c>
-      <c r="C101">
-        <v>699.0063949057871</v>
-      </c>
-      <c r="D101">
-        <v>2051.032394905787</v>
-      </c>
-      <c r="E101">
-        <v>1050.826</v>
-      </c>
-      <c r="F101">
-        <v>1442.826</v>
-      </c>
-      <c r="G101">
-        <v>90.8</v>
-      </c>
-      <c r="H101">
-        <v>1065.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>348.9999999999999</v>
-      </c>
-      <c r="K101">
-        <v>55.39999999999998</v>
-      </c>
-      <c r="L101">
-        <v>293.6</v>
-      </c>
-      <c r="M101">
-        <v>92.48514660000001</v>
-      </c>
-      <c r="N101">
-        <v>201.1148534</v>
-      </c>
-      <c r="O101">
-        <v>60.33445601999998</v>
-      </c>
-      <c r="P101">
-        <v>140.78039738</v>
-      </c>
-      <c r="Q101">
-        <v>196.18039738</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>7.013774455915923</v>
-      </c>
-      <c r="T101">
-        <v>48.58380161750903</v>
-      </c>
-      <c r="U101">
-        <v>0.0641</v>
-      </c>
-      <c r="V101">
-        <v>0.3</v>
-      </c>
-      <c r="W101">
-        <v>0.04487</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ba2/BB</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>3.174563816931874</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
